--- a/src/attributions/attributions_saliency_traj_316.xlsx
+++ b/src/attributions/attributions_saliency_traj_316.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7.516846380895004e-06</v>
+        <v>3.914996327125664e-08</v>
       </c>
       <c r="B4" t="n">
-        <v>3.824716623057611e-05</v>
+        <v>3.892049704745659e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.057896148879081e-06</v>
+        <v>4.528229169409315e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.825132575409953e-06</v>
+        <v>1.299566232404459e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.398293872829527e-06</v>
+        <v>8.183828725805142e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>3.080751412198879e-05</v>
+        <v>4.423515775897613e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66256472261739e-07</v>
+        <v>3.331354037072742e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.327307007974014e-06</v>
+        <v>1.147923978095378e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08230903808726e-06</v>
+        <v>3.527233838340749e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.304485158470925e-05</v>
+        <v>1.690999695824758e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.880591637222096e-05</v>
+        <v>8.054227507159339e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.034095475915819e-06</v>
+        <v>5.288089255373052e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.423776317707961e-06</v>
+        <v>8.428845177377298e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.954799128929153e-06</v>
+        <v>8.096140646784988e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>2.038394450210035e-05</v>
+        <v>1.025056217685005e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.186106939916499e-06</v>
+        <v>5.388190160715567e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.054821404977702e-05</v>
+        <v>2.380270647250882e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.720526809862349e-06</v>
+        <v>1.489009449073819e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.328546886725235e-06</v>
+        <v>1.682266059788162e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.706726718315622e-06</v>
+        <v>3.434176321093219e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>9.00390020319719e-08</v>
+        <v>1.164567997591348e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>4.391126822156366e-06</v>
+        <v>6.318340517452725e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.444387615076266e-06</v>
+        <v>3.511675572553941e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.994311439077137e-06</v>
+        <v>5.184942253322333e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.131982455466641e-06</v>
+        <v>1.740198030120155e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.115252068004338e-06</v>
+        <v>8.712991217407762e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.155688189821376e-07</v>
+        <v>1.293309015437671e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.303252358615282e-06</v>
+        <v>3.153265737410038e-08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.014540143591148e-07</v>
+        <v>1.211000855150246e-09</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32116372242308e-06</v>
+        <v>1.142470562598419e-08</v>
       </c>
       <c r="AE4" t="n">
-        <v>7.254679076140746e-06</v>
+        <v>2.295296219756437e-08</v>
       </c>
       <c r="AF4" t="n">
-        <v>6.270433004829101e-06</v>
+        <v>1.504332658441854e-08</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.816711685227347e-06</v>
+        <v>3.736851894586835e-08</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.370715593424393e-07</v>
+        <v>1.121503601098084e-08</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.434269279343425e-06</v>
+        <v>5.919450707381202e-09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6.285809490691463e-07</v>
+        <v>3.213243893185336e-09</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.004558155022096e-07</v>
+        <v>1.255791293175434e-08</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.317112830496626e-06</v>
+        <v>1.401183258309402e-08</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.076380264450563e-06</v>
+        <v>6.90290224980572e-09</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.475346031540539e-06</v>
+        <v>1.284383177591053e-08</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.92317975233891e-06</v>
+        <v>2.261408482695515e-08</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.252278919622768e-06</v>
+        <v>1.230363810833524e-09</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.953448751621181e-06</v>
+        <v>7.737907203875238e-09</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.87408351546037e-06</v>
+        <v>8.986050126225109e-09</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.815846740617417e-06</v>
+        <v>5.626557553206624e-10</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.763424830249278e-07</v>
+        <v>8.178107080425434e-09</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.654225707170554e-05</v>
+        <v>3.668323600436452e-08</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.172155503416434e-06</v>
+        <v>2.851795777303323e-08</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.681872047105571e-06</v>
+        <v>1.222030809877594e-10</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.391420028085122e-07</v>
+        <v>1.929431903135992e-08</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.784939953126013e-06</v>
+        <v>7.021574432997113e-09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.014246663544327e-05</v>
+        <v>1.289976836460482e-08</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.355819212127244e-06</v>
+        <v>1.617796563380125e-08</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.326755500485888e-05</v>
+        <v>6.490887827226288e-09</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.083918141375761e-05</v>
+        <v>2.089255879411667e-08</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.354282388405409e-06</v>
+        <v>3.7955274478918e-09</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.100418780377368e-06</v>
+        <v>2.605856153081731e-08</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.413821094814921e-07</v>
+        <v>7.337507934579435e-09</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.67484538705321e-06</v>
+        <v>2.158727596679455e-08</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.518207500339486e-05</v>
+        <v>2.740727644834351e-09</v>
       </c>
       <c r="BI4" t="n">
-        <v>9.480625521973707e-06</v>
+        <v>6.767321814038496e-09</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4.542803708318388e-06</v>
+        <v>8.190583322686962e-09</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.290988600696437e-06</v>
+        <v>7.613176755683071e-09</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.202397697852575e-06</v>
+        <v>2.566612877785701e-08</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.261759489869291e-07</v>
+        <v>1.282210249087257e-08</v>
       </c>
       <c r="BN4" t="n">
-        <v>8.661127139930613e-07</v>
+        <v>1.436373331387131e-08</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.160198848992877e-06</v>
+        <v>1.644050051652357e-08</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.398871846613474e-06</v>
+        <v>1.470925070634621e-08</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.750371201429516e-07</v>
+        <v>1.080406608622297e-08</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.467949227342615e-06</v>
+        <v>8.392299299941897e-09</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.150419161102036e-07</v>
+        <v>2.042097690946321e-08</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.397442014829721e-06</v>
+        <v>1.668952442912541e-08</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.606001544336323e-06</v>
+        <v>5.905531175187662e-09</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.075519230653299e-05</v>
+        <v>1.621379297489511e-08</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.980171075250837e-06</v>
+        <v>6.033283650452859e-09</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.744171413520235e-06</v>
+        <v>4.328018832211455e-08</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.335624337021727e-06</v>
+        <v>2.626477701994645e-08</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.599633823294425e-06</v>
+        <v>1.441784247546707e-09</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.156343500952062e-06</v>
+        <v>3.878080079289248e-09</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.145525741070742e-06</v>
+        <v>5.225593291413588e-09</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.12461247126339e-06</v>
+        <v>3.818195537519387e-09</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.73270359482558e-06</v>
+        <v>5.284662485394165e-09</v>
       </c>
       <c r="CE4" t="n">
-        <v>5.245710781309754e-06</v>
+        <v>9.471987638676183e-09</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.304281906617689e-06</v>
+        <v>1.165849994322343e-08</v>
       </c>
       <c r="CG4" t="n">
-        <v>7.753621957817813e-07</v>
+        <v>1.325760723425162e-09</v>
       </c>
       <c r="CH4" t="n">
-        <v>3.467278020252706e-06</v>
+        <v>5.328767205270424e-09</v>
       </c>
       <c r="CI4" t="n">
-        <v>5.719370619772235e-06</v>
+        <v>2.402184451355538e-09</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.218142299170722e-06</v>
+        <v>7.44958428278153e-10</v>
       </c>
       <c r="CK4" t="n">
-        <v>6.328808126454533e-07</v>
+        <v>3.040600660142445e-09</v>
       </c>
       <c r="CL4" t="n">
-        <v>4.130007255298551e-06</v>
+        <v>1.344291522542562e-08</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.498040541671799e-06</v>
+        <v>2.54921772580019e-08</v>
       </c>
       <c r="CN4" t="n">
-        <v>5.63905450690072e-06</v>
+        <v>3.661554615064233e-08</v>
       </c>
       <c r="CO4" t="n">
-        <v>4.986268777429359e-06</v>
+        <v>1.158731421924131e-08</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.678612407995388e-06</v>
+        <v>1.49135210847362e-08</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.516245098784566e-06</v>
+        <v>8.415704577657834e-09</v>
       </c>
       <c r="CR4" t="n">
-        <v>7.211818910946022e-07</v>
+        <v>7.80057440863402e-09</v>
       </c>
       <c r="CS4" t="n">
-        <v>4.080879079992883e-06</v>
+        <v>2.158743939162378e-08</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.416708977965754e-07</v>
+        <v>2.094689399712024e-08</v>
       </c>
       <c r="CU4" t="n">
-        <v>9.233110176865011e-06</v>
+        <v>1.083896972176035e-08</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.146501631410501e-06</v>
+        <v>5.775942835128944e-09</v>
       </c>
       <c r="CW4" t="n">
-        <v>6.381809726008214e-06</v>
+        <v>9.185605165384914e-09</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.472557187298662e-06</v>
+        <v>1.125155701942049e-08</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.605743932486803e-06</v>
+        <v>4.120225050030513e-09</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.213689862808678e-06</v>
+        <v>3.822495209249155e-09</v>
       </c>
       <c r="DA4" t="n">
-        <v>5.753622644988354e-06</v>
+        <v>5.841523931238157e-10</v>
       </c>
       <c r="DB4" t="n">
-        <v>9.283039617002942e-07</v>
+        <v>4.92300777921173e-09</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.667817966539587e-07</v>
+        <v>8.484867031199883e-09</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.341020940046292e-06</v>
+        <v>1.114557957038187e-08</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.212645995314233e-06</v>
+        <v>2.131144327677248e-08</v>
       </c>
       <c r="DF4" t="n">
-        <v>4.274361344869249e-06</v>
+        <v>3.749700638877584e-08</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.892904831242049e-06</v>
+        <v>1.467308496927444e-09</v>
       </c>
       <c r="DH4" t="n">
-        <v>7.515820470871404e-06</v>
+        <v>2.309774060904601e-08</v>
       </c>
       <c r="DI4" t="n">
-        <v>5.49987498743576e-06</v>
+        <v>2.680571320468061e-10</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.902186886582058e-05</v>
+        <v>4.162620115266691e-08</v>
       </c>
       <c r="DK4" t="n">
-        <v>8.279879693873227e-06</v>
+        <v>1.067554578071395e-08</v>
       </c>
       <c r="DL4" t="n">
-        <v>4.084095053258352e-07</v>
+        <v>1.29836612572376e-08</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.369132132822415e-05</v>
+        <v>5.893294741099453e-10</v>
       </c>
       <c r="DN4" t="n">
-        <v>4.759025159728481e-06</v>
+        <v>2.171530510963748e-08</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.688844688236713e-06</v>
+        <v>4.768137884525459e-09</v>
       </c>
       <c r="DP4" t="n">
-        <v>1.171605049421487e-06</v>
+        <v>1.094150192670895e-08</v>
       </c>
       <c r="DQ4" t="n">
-        <v>4.732635716209188e-06</v>
+        <v>3.248424818025342e-08</v>
       </c>
       <c r="DR4" t="n">
-        <v>2.707739440666046e-06</v>
+        <v>2.228025097750219e-09</v>
       </c>
       <c r="DS4" t="n">
-        <v>2.950692987724324e-07</v>
+        <v>2.284813938047137e-08</v>
       </c>
       <c r="DT4" t="n">
-        <v>8.126400643959641e-06</v>
+        <v>9.703395420501693e-09</v>
       </c>
       <c r="DU4" t="n">
-        <v>7.307114628929412e-07</v>
+        <v>4.847916290628973e-09</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.868014462364954e-06</v>
+        <v>8.282842856033312e-09</v>
       </c>
       <c r="DW4" t="n">
-        <v>2.760142706392799e-06</v>
+        <v>8.161247677662686e-09</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.804757289392001e-06</v>
+        <v>7.867444473674823e-09</v>
       </c>
       <c r="DY4" t="n">
-        <v>1.480102582718246e-07</v>
+        <v>2.509300145447924e-08</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.936420969490428e-06</v>
+        <v>1.064853538679245e-08</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.444277015456464e-06</v>
+        <v>1.633768675901592e-08</v>
       </c>
       <c r="EB4" t="n">
-        <v>5.227783503869432e-07</v>
+        <v>1.252730541523306e-08</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.601870164653519e-06</v>
+        <v>6.841612609775893e-09</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.269338544167113e-06</v>
+        <v>6.890195081155071e-09</v>
       </c>
       <c r="EE4" t="n">
-        <v>4.990287379769143e-06</v>
+        <v>6.461905677213053e-09</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.929474365169881e-06</v>
+        <v>3.555384431308539e-09</v>
       </c>
       <c r="EG4" t="n">
-        <v>3.741193268069765e-06</v>
+        <v>1.03575009680057e-10</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.555335640863632e-07</v>
+        <v>9.538632106398381e-10</v>
       </c>
       <c r="EI4" t="n">
-        <v>6.817635949118994e-06</v>
+        <v>2.115290165249917e-09</v>
       </c>
       <c r="EJ4" t="n">
-        <v>4.985731266060611e-06</v>
+        <v>1.386308401407632e-08</v>
       </c>
       <c r="EK4" t="n">
-        <v>3.026917511306237e-06</v>
+        <v>8.661999117975938e-09</v>
       </c>
       <c r="EL4" t="n">
-        <v>4.012056251667673e-06</v>
+        <v>3.775842749575986e-09</v>
       </c>
       <c r="EM4" t="n">
-        <v>2.016124511783346e-07</v>
+        <v>1.238688374094465e-09</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.594413333805278e-06</v>
+        <v>1.312332820191386e-08</v>
       </c>
       <c r="EO4" t="n">
-        <v>2.8451588605094e-06</v>
+        <v>1.214639944180362e-08</v>
       </c>
       <c r="EP4" t="n">
-        <v>3.089897290919907e-06</v>
+        <v>1.85754078785294e-08</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.579212721480872e-06</v>
+        <v>1.004174698948646e-08</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.931969336510519e-06</v>
+        <v>2.046047775650095e-08</v>
       </c>
       <c r="ES4" t="n">
-        <v>1.004420118988492e-05</v>
+        <v>1.321241871465872e-08</v>
       </c>
       <c r="ET4" t="n">
-        <v>1.518047247373033e-05</v>
+        <v>6.830431775739498e-09</v>
       </c>
       <c r="EU4" t="n">
-        <v>5.969236099190312e-06</v>
+        <v>3.962686179193042e-09</v>
       </c>
       <c r="EV4" t="n">
-        <v>3.961705715482822e-06</v>
+        <v>3.868755094060816e-09</v>
       </c>
       <c r="EW4" t="n">
-        <v>7.735461622360162e-06</v>
+        <v>7.430675630359929e-09</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.266485355699842e-06</v>
+        <v>3.417050198351035e-09</v>
       </c>
       <c r="EY4" t="n">
-        <v>6.440875949920155e-06</v>
+        <v>7.558233150462002e-09</v>
       </c>
       <c r="EZ4" t="n">
-        <v>4.41362715264404e-07</v>
+        <v>9.148720891971607e-09</v>
       </c>
       <c r="FA4" t="n">
-        <v>4.017731498606736e-07</v>
+        <v>5.134420888452951e-09</v>
       </c>
       <c r="FB4" t="n">
-        <v>5.044013505539624e-06</v>
+        <v>8.484768443395296e-12</v>
       </c>
       <c r="FC4" t="n">
-        <v>4.488524609769229e-06</v>
+        <v>1.984381103881105e-09</v>
       </c>
       <c r="FD4" t="n">
-        <v>3.291292841822724e-06</v>
+        <v>1.977341179681957e-09</v>
       </c>
       <c r="FE4" t="n">
-        <v>4.248107075000007e-07</v>
+        <v>4.264780972818016e-09</v>
       </c>
       <c r="FF4" t="n">
-        <v>6.08136997470865e-06</v>
+        <v>7.207723307089964e-09</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.922570845636073e-06</v>
+        <v>3.036194939909365e-08</v>
       </c>
       <c r="FH4" t="n">
-        <v>3.573768026399193e-06</v>
+        <v>1.073504840576334e-08</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.087562390646781e-06</v>
+        <v>8.199144474474451e-09</v>
       </c>
       <c r="FJ4" t="n">
-        <v>4.887662726105191e-06</v>
+        <v>7.524935341507444e-09</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.206581484642811e-06</v>
+        <v>3.504564416445533e-09</v>
       </c>
       <c r="FL4" t="n">
-        <v>3.285620095994091e-06</v>
+        <v>3.76320699047028e-08</v>
       </c>
       <c r="FM4" t="n">
-        <v>2.695408511499409e-06</v>
+        <v>3.323438191316086e-09</v>
       </c>
       <c r="FN4" t="n">
-        <v>2.287517645527259e-06</v>
+        <v>3.005031956604398e-08</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.355133912918973e-06</v>
+        <v>3.231824408089778e-08</v>
       </c>
       <c r="FP4" t="n">
-        <v>8.29880036690156e-07</v>
+        <v>6.583117162506369e-09</v>
       </c>
       <c r="FQ4" t="n">
-        <v>5.952913852524944e-06</v>
+        <v>2.790024211662967e-09</v>
       </c>
       <c r="FR4" t="n">
-        <v>5.208170023252023e-06</v>
+        <v>3.962446726291091e-08</v>
       </c>
       <c r="FS4" t="n">
-        <v>2.442303411953617e-06</v>
+        <v>1.607510347056973e-09</v>
       </c>
       <c r="FT4" t="n">
-        <v>2.825772753567435e-06</v>
+        <v>2.429427325978395e-08</v>
       </c>
       <c r="FU4" t="n">
-        <v>1.169834558822913e-05</v>
+        <v>1.086151701912286e-08</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.284297124788282e-06</v>
+        <v>5.792195167941827e-08</v>
       </c>
       <c r="FW4" t="n">
-        <v>4.29664623879944e-06</v>
+        <v>1.4244208479397e-08</v>
       </c>
       <c r="FX4" t="n">
-        <v>4.285603608877864e-06</v>
+        <v>2.020826528337238e-08</v>
       </c>
       <c r="FY4" t="n">
-        <v>4.794907454197528e-06</v>
+        <v>7.070022345345706e-09</v>
       </c>
       <c r="FZ4" t="n">
-        <v>5.295715709507931e-06</v>
+        <v>1.737064536655453e-08</v>
       </c>
       <c r="GA4" t="n">
-        <v>1.217682097376382e-06</v>
+        <v>3.780106450079757e-09</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.613842298160307e-06</v>
+        <v>9.283354529543431e-09</v>
       </c>
       <c r="GC4" t="n">
-        <v>1.071957558451686e-05</v>
+        <v>8.187552857918945e-09</v>
       </c>
       <c r="GD4" t="n">
-        <v>6.754836476829951e-07</v>
+        <v>2.559946699065563e-09</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.842560095610679e-06</v>
+        <v>2.179090508036552e-08</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.828251356528199e-06</v>
+        <v>5.838111327705064e-09</v>
       </c>
       <c r="GG4" t="n">
-        <v>3.239333409510436e-06</v>
+        <v>9.080751262047215e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.885370334610343e-05</v>
+        <v>0.0005906212609261274</v>
       </c>
       <c r="B5" t="n">
-        <v>9.979616152122617e-05</v>
+        <v>0.07572384923696518</v>
       </c>
       <c r="C5" t="n">
-        <v>5.16781146870926e-05</v>
+        <v>0.01161371730268002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002038491074927151</v>
+        <v>0.05224595218896866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002324177330592647</v>
+        <v>0.001861446886323392</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001014374720398337</v>
+        <v>0.003497895086184144</v>
       </c>
       <c r="G5" t="n">
-        <v>7.29275998310186e-05</v>
+        <v>0.04023490473628044</v>
       </c>
       <c r="H5" t="n">
-        <v>6.646430847467855e-05</v>
+        <v>0.02559309080243111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001737160782795399</v>
+        <v>0.01489981543272734</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001099180954042822</v>
+        <v>0.009175896644592285</v>
       </c>
       <c r="K5" t="n">
-        <v>5.626125494018197e-05</v>
+        <v>0.07040811330080032</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001029070117510855</v>
+        <v>0.02025064453482628</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002838973596226424</v>
+        <v>0.07361602783203125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003850472567137331</v>
+        <v>0.02541794441640377</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001777047000359744</v>
+        <v>0.007490263320505619</v>
       </c>
       <c r="P5" t="n">
-        <v>1.024940138449892e-05</v>
+        <v>0.03284022212028503</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.601625626790337e-05</v>
+        <v>0.004981614649295807</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002276129671372473</v>
+        <v>0.008995616808533669</v>
       </c>
       <c r="S5" t="n">
-        <v>1.354138112219516e-05</v>
+        <v>0.001899756491184235</v>
       </c>
       <c r="T5" t="n">
-        <v>1.35486334329471e-06</v>
+        <v>0.01044515799731016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001102427777368575</v>
+        <v>9.961659088730812e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.648559191380627e-05</v>
+        <v>0.00499453954398632</v>
       </c>
       <c r="W5" t="n">
-        <v>3.869759893859737e-05</v>
+        <v>0.01207085698843002</v>
       </c>
       <c r="X5" t="n">
-        <v>9.398402471560985e-05</v>
+        <v>0.01253361813724041</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.528645488084294e-05</v>
+        <v>0.01055629178881645</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.895086986944079e-05</v>
+        <v>0.02663471177220345</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001527443964732811</v>
+        <v>0.003989148885011673</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.915014091646299e-05</v>
+        <v>0.0009716718923300505</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.537467121845111e-06</v>
+        <v>0.004082291387021542</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001822140184231102</v>
+        <v>0.00804544985294342</v>
       </c>
       <c r="AE5" t="n">
-        <v>9.691072773421183e-05</v>
+        <v>0.01547773275524378</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.82646452030167e-05</v>
+        <v>0.005010009277611971</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.128630851279013e-05</v>
+        <v>0.03854190930724144</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.56385810644133e-05</v>
+        <v>0.003441923763602972</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.198141944769304e-05</v>
+        <v>0.01655765436589718</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001941614027600735</v>
+        <v>0.006100649014115334</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.298744508763775e-05</v>
+        <v>0.003901032730937004</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.39532518107444e-05</v>
+        <v>0.02442616783082485</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.308781793341041e-05</v>
+        <v>0.008528605103492737</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.815963155939244e-06</v>
+        <v>0.004997742362320423</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001560213277116418</v>
+        <v>0.01877139322459698</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.000117311836220324</v>
+        <v>0.01237467210739851</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.066196273313835e-05</v>
+        <v>0.006102216895669699</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.834134597331285e-05</v>
+        <v>0.0003315502544865012</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.532520400360227e-06</v>
+        <v>0.004723980091512203</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.535321098344866e-05</v>
+        <v>0.001760098035447299</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0002458301023580134</v>
+        <v>0.03089751675724983</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.267492426559329e-05</v>
+        <v>0.00847929809242487</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.841142461169511e-05</v>
+        <v>0.02028110809624195</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.000191457336768508</v>
+        <v>0.04996485263109207</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0001072209852281958</v>
+        <v>0.01952564157545567</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.877473449800164e-05</v>
+        <v>0.001071969396434724</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.609570457134396e-05</v>
+        <v>0.0001823777856770903</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0002531269856262952</v>
+        <v>0.009494556114077568</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0001326137571595609</v>
+        <v>0.01188158430159092</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0001027614853228442</v>
+        <v>0.005886184051632881</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.167469574487768e-05</v>
+        <v>0.01319025922566652</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.11036622710526e-05</v>
+        <v>0.001854271627962589</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.335585203487426e-05</v>
+        <v>0.02372514083981514</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.287651482736692e-05</v>
+        <v>2.896843943744898e-05</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001028049155138433</v>
+        <v>0.01331101078540087</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5.348127888282761e-05</v>
+        <v>0.03460804000496864</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003616656176745892</v>
+        <v>0.003490107366815209</v>
       </c>
       <c r="BL5" t="n">
-        <v>8.338282350450754e-05</v>
+        <v>0.0005054360954090953</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.951374881376978e-05</v>
+        <v>0.01662821508944035</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.374690666329116e-06</v>
+        <v>0.007330071646720171</v>
       </c>
       <c r="BO5" t="n">
-        <v>9.645652608014643e-05</v>
+        <v>0.01294311601668596</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0002696386654861271</v>
+        <v>0.01108797546476126</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.356504359748214e-05</v>
+        <v>0.001026697573252022</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.626670513767749e-05</v>
+        <v>0.006018084473907948</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.44131216884125e-05</v>
+        <v>0.006023922935128212</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.413525549462065e-05</v>
+        <v>0.01131485588848591</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.196698111831211e-06</v>
+        <v>0.002220178488641977</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0001385243376716971</v>
+        <v>0.02768145874142647</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.318306597881019e-05</v>
+        <v>0.009140900336205959</v>
       </c>
       <c r="BX5" t="n">
-        <v>1.063531635736581e-05</v>
+        <v>0.02713353559374809</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.452991460217163e-05</v>
+        <v>0.001704073627479374</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.919700636994094e-05</v>
+        <v>0.01025474537163973</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.57703429472167e-05</v>
+        <v>0.01172110810875893</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.84927807317581e-05</v>
+        <v>0.005029229912906885</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0002392769820289686</v>
+        <v>0.002872970653697848</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.83187725674361e-05</v>
+        <v>0.0008583082817494869</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.937655179062858e-05</v>
+        <v>0.02332065999507904</v>
       </c>
       <c r="CF5" t="n">
-        <v>6.996742740739137e-06</v>
+        <v>0.0009752619080245495</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.06906897801673e-05</v>
+        <v>0.02247552014887333</v>
       </c>
       <c r="CH5" t="n">
-        <v>2.925687113020103e-05</v>
+        <v>0.002640001010149717</v>
       </c>
       <c r="CI5" t="n">
-        <v>6.870523793622851e-05</v>
+        <v>0.001381044625304639</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.879884621303063e-06</v>
+        <v>0.003136634826660156</v>
       </c>
       <c r="CK5" t="n">
-        <v>5.284718645270914e-05</v>
+        <v>0.0007467232644557953</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0001295622641919181</v>
+        <v>0.002136388327926397</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0001411858684150502</v>
+        <v>0.00824869517236948</v>
       </c>
       <c r="CN5" t="n">
-        <v>4.095022813999094e-05</v>
+        <v>0.009072430431842804</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.641144262976013e-05</v>
+        <v>0.0262807197868824</v>
       </c>
       <c r="CP5" t="n">
-        <v>5.910748222959228e-05</v>
+        <v>0.04039870575070381</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0003003351157531142</v>
+        <v>0.0003456058329902589</v>
       </c>
       <c r="CR5" t="n">
-        <v>3.788110916502774e-06</v>
+        <v>0.01321045495569706</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.785592758096755e-05</v>
+        <v>0.02309366129338741</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001232521317433566</v>
+        <v>0.01349256653338671</v>
       </c>
       <c r="CU5" t="n">
-        <v>6.441932782763615e-05</v>
+        <v>0.003285122802481055</v>
       </c>
       <c r="CV5" t="n">
-        <v>3.648655547294766e-05</v>
+        <v>0.0007435408188030124</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.069497713819146e-05</v>
+        <v>0.02248185873031616</v>
       </c>
       <c r="CX5" t="n">
-        <v>2.697495801839978e-05</v>
+        <v>0.002699089236557484</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.649888145038858e-05</v>
+        <v>0.02367059886455536</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.87056464003399e-05</v>
+        <v>0.00168489501811564</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001076959088095464</v>
+        <v>0.0002747795078903437</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.225992127729114e-05</v>
+        <v>0.00372731895186007</v>
       </c>
       <c r="DC5" t="n">
-        <v>5.489067007147241e-06</v>
+        <v>0.001429185969755054</v>
       </c>
       <c r="DD5" t="n">
-        <v>9.351410699309781e-05</v>
+        <v>0.001004607416689396</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.874534013448283e-05</v>
+        <v>0.005641810595989227</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0001066018303390592</v>
+        <v>0.01901575177907944</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.576396895572543e-05</v>
+        <v>0.002862129593268037</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0001953159953700379</v>
+        <v>0.02895574271678925</v>
       </c>
       <c r="DI5" t="n">
-        <v>5.826410779263824e-05</v>
+        <v>0.01066209468990564</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.000165723540703766</v>
+        <v>0.02030286937952042</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.888468199875206e-05</v>
+        <v>0.001473743002861738</v>
       </c>
       <c r="DL5" t="n">
-        <v>6.371257768478245e-05</v>
+        <v>0.03364396840333939</v>
       </c>
       <c r="DM5" t="n">
-        <v>3.28860551235266e-06</v>
+        <v>0.007294018287211657</v>
       </c>
       <c r="DN5" t="n">
-        <v>5.499799044628162e-06</v>
+        <v>0.0004214002983644605</v>
       </c>
       <c r="DO5" t="n">
-        <v>5.505403169081546e-05</v>
+        <v>0.009426971897482872</v>
       </c>
       <c r="DP5" t="n">
-        <v>2.337477417313494e-05</v>
+        <v>0.002418281976133585</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.669432094786316e-06</v>
+        <v>0.01519503723829985</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.944457810372114e-05</v>
+        <v>0.002765416167676449</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.582060162443668e-05</v>
+        <v>0.002793281571939588</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001100467125070281</v>
+        <v>0.02108044177293777</v>
       </c>
       <c r="DU5" t="n">
-        <v>2.054216201941017e-05</v>
+        <v>0.003356584580615163</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0001654098596191034</v>
+        <v>0.03168715536594391</v>
       </c>
       <c r="DW5" t="n">
-        <v>5.062422133050859e-05</v>
+        <v>7.438771717716008e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.622931298101321e-05</v>
+        <v>0.001889588078483939</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.679126479662955e-05</v>
+        <v>0.01291078329086304</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.954014598799404e-05</v>
+        <v>0.001233423128724098</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.576489739818498e-05</v>
+        <v>0.0004166190046817064</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001789877569535747</v>
+        <v>0.00556141696870327</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.280060314456932e-05</v>
+        <v>0.004221393261104822</v>
       </c>
       <c r="ED5" t="n">
-        <v>3.25261389662046e-05</v>
+        <v>0.04063120484352112</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.655876621953212e-05</v>
+        <v>0.02401022985577583</v>
       </c>
       <c r="EF5" t="n">
-        <v>6.814076186856255e-06</v>
+        <v>0.008278129622340202</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.938263009535149e-05</v>
+        <v>0.01759917661547661</v>
       </c>
       <c r="EH5" t="n">
-        <v>4.788985097547993e-05</v>
+        <v>0.00883601326495409</v>
       </c>
       <c r="EI5" t="n">
-        <v>5.956141831120476e-05</v>
+        <v>0.0282724667340517</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0001078066125046462</v>
+        <v>0.009275901131331921</v>
       </c>
       <c r="EK5" t="n">
-        <v>6.912828393978998e-05</v>
+        <v>0.007915358990430832</v>
       </c>
       <c r="EL5" t="n">
-        <v>5.858559597982094e-05</v>
+        <v>0.004212155938148499</v>
       </c>
       <c r="EM5" t="n">
-        <v>3.773695425479673e-05</v>
+        <v>0.00500588770955801</v>
       </c>
       <c r="EN5" t="n">
-        <v>8.714318391866982e-05</v>
+        <v>0.002225751988589764</v>
       </c>
       <c r="EO5" t="n">
-        <v>3.804158768616617e-05</v>
+        <v>0.004146130289882421</v>
       </c>
       <c r="EP5" t="n">
-        <v>5.338892879080959e-05</v>
+        <v>0.02784394100308418</v>
       </c>
       <c r="EQ5" t="n">
-        <v>3.987537638749927e-05</v>
+        <v>0.008616087958216667</v>
       </c>
       <c r="ER5" t="n">
-        <v>6.697633580188267e-06</v>
+        <v>0.01103473640978336</v>
       </c>
       <c r="ES5" t="n">
-        <v>3.875582478940487e-06</v>
+        <v>0.006750554777681828</v>
       </c>
       <c r="ET5" t="n">
-        <v>6.75408446113579e-05</v>
+        <v>0.008196872659027576</v>
       </c>
       <c r="EU5" t="n">
-        <v>9.504622539679985e-06</v>
+        <v>0.01075180899351835</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0001089771321858279</v>
+        <v>0.0003495151177048683</v>
       </c>
       <c r="EW5" t="n">
-        <v>8.388971764361486e-06</v>
+        <v>0.009752450510859489</v>
       </c>
       <c r="EX5" t="n">
-        <v>6.015790131641552e-05</v>
+        <v>0.001120084896683693</v>
       </c>
       <c r="EY5" t="n">
-        <v>4.350442031864077e-05</v>
+        <v>0.02321805618703365</v>
       </c>
       <c r="EZ5" t="n">
-        <v>2.944461630249862e-05</v>
+        <v>0.001889974344521761</v>
       </c>
       <c r="FA5" t="n">
-        <v>1.702582085272297e-05</v>
+        <v>0.02893667854368687</v>
       </c>
       <c r="FB5" t="n">
-        <v>5.830383088323288e-05</v>
+        <v>0.0004700981080532074</v>
       </c>
       <c r="FC5" t="n">
-        <v>3.932198887923732e-05</v>
+        <v>0.001043297117576003</v>
       </c>
       <c r="FD5" t="n">
-        <v>2.576706356194336e-05</v>
+        <v>0.0007667542668059468</v>
       </c>
       <c r="FE5" t="n">
-        <v>4.842209455091506e-05</v>
+        <v>0.0003661539521999657</v>
       </c>
       <c r="FF5" t="n">
-        <v>8.691353286849335e-05</v>
+        <v>0.003038162831217051</v>
       </c>
       <c r="FG5" t="n">
-        <v>2.929029142251238e-05</v>
+        <v>0.008204404264688492</v>
       </c>
       <c r="FH5" t="n">
-        <v>8.470085595035926e-05</v>
+        <v>0.006093117408454418</v>
       </c>
       <c r="FI5" t="n">
-        <v>4.65047123725526e-05</v>
+        <v>0.009544181637465954</v>
       </c>
       <c r="FJ5" t="n">
-        <v>1.53558466990944e-05</v>
+        <v>0.01918806880712509</v>
       </c>
       <c r="FK5" t="n">
-        <v>3.374866355443373e-05</v>
+        <v>0.008803953416645527</v>
       </c>
       <c r="FL5" t="n">
-        <v>7.865849329391494e-05</v>
+        <v>0.007951554842293262</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.730766472173855e-06</v>
+        <v>0.002112566027790308</v>
       </c>
       <c r="FN5" t="n">
-        <v>7.418000313919038e-05</v>
+        <v>0.01633138209581375</v>
       </c>
       <c r="FO5" t="n">
-        <v>5.036874426878057e-05</v>
+        <v>0.006150323897600174</v>
       </c>
       <c r="FP5" t="n">
-        <v>9.220117499353364e-05</v>
+        <v>0.01532486360520124</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001892726286314428</v>
+        <v>0.02578114718198776</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.204059172887355e-05</v>
+        <v>0.002961522899568081</v>
       </c>
       <c r="FS5" t="n">
-        <v>1.817689189920202e-05</v>
+        <v>0.00123892817646265</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.000396388495573774</v>
+        <v>0.01702164113521576</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001941866794368252</v>
+        <v>0.02643034979701042</v>
       </c>
       <c r="FV5" t="n">
-        <v>4.128685759496875e-05</v>
+        <v>0.009154669009149075</v>
       </c>
       <c r="FW5" t="n">
-        <v>5.708161188522354e-05</v>
+        <v>0.002706962404772639</v>
       </c>
       <c r="FX5" t="n">
-        <v>1.597856862645131e-05</v>
+        <v>0.03382325172424316</v>
       </c>
       <c r="FY5" t="n">
-        <v>6.754853529855609e-07</v>
+        <v>0.008962618187069893</v>
       </c>
       <c r="FZ5" t="n">
-        <v>3.567986277630553e-05</v>
+        <v>0.007928295992314816</v>
       </c>
       <c r="GA5" t="n">
-        <v>9.801245323615149e-05</v>
+        <v>0.007604182232171297</v>
       </c>
       <c r="GB5" t="n">
-        <v>5.834964395035058e-05</v>
+        <v>0.02691062539815903</v>
       </c>
       <c r="GC5" t="n">
-        <v>9.946624777512625e-05</v>
+        <v>0.003434692742303014</v>
       </c>
       <c r="GD5" t="n">
-        <v>6.581303023267537e-05</v>
+        <v>0.005362866446375847</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0001387504598824307</v>
+        <v>0.01639773137867451</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001579101226525381</v>
+        <v>0.001765045686624944</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0001205590015160851</v>
+        <v>0.0004108052235096693</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.973732196347555e-06</v>
+        <v>1.712886695546048e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.866196038870839e-06</v>
+        <v>6.20429055353533e-13</v>
       </c>
       <c r="C6" t="n">
-        <v>5.444828730105655e-07</v>
+        <v>2.936826129507075e-13</v>
       </c>
       <c r="D6" t="n">
-        <v>3.508570216581575e-06</v>
+        <v>9.645532799123363e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>4.497519967117114e-06</v>
+        <v>5.518877455729099e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>4.849621291214135e-06</v>
+        <v>1.116667413918193e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>3.299728859929019e-06</v>
+        <v>9.820127567020109e-13</v>
       </c>
       <c r="H6" t="n">
-        <v>7.992010750967893e-07</v>
+        <v>1.3147832432156e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>7.350062332989182e-06</v>
+        <v>2.643470837192241e-13</v>
       </c>
       <c r="J6" t="n">
-        <v>2.422062152618309e-06</v>
+        <v>3.539272553417655e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>6.437664069380844e-06</v>
+        <v>2.959082089602771e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>9.269915608456358e-07</v>
+        <v>5.933329457093184e-13</v>
       </c>
       <c r="M6" t="n">
-        <v>9.753380254551303e-07</v>
+        <v>4.161298042260064e-13</v>
       </c>
       <c r="N6" t="n">
-        <v>4.818592969968449e-06</v>
+        <v>8.766598016095306e-13</v>
       </c>
       <c r="O6" t="n">
-        <v>2.373132929278654e-06</v>
+        <v>1.579748267963033e-12</v>
       </c>
       <c r="P6" t="n">
-        <v>7.41106077839504e-07</v>
+        <v>1.423357634013078e-12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.452571607136633e-06</v>
+        <v>1.536808766182396e-12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.72111526808294e-06</v>
+        <v>4.049278273798862e-14</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55230281961849e-06</v>
+        <v>2.323223807342706e-13</v>
       </c>
       <c r="T6" t="n">
-        <v>1.298779125136207e-06</v>
+        <v>4.110206912235487e-13</v>
       </c>
       <c r="U6" t="n">
-        <v>1.970392986549996e-07</v>
+        <v>4.725985770261121e-14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.497765879321378e-06</v>
+        <v>5.99991302301095e-13</v>
       </c>
       <c r="W6" t="n">
-        <v>3.258658125560032e-06</v>
+        <v>8.722369072670932e-13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.152735933374061e-07</v>
+        <v>1.814337932280405e-13</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.712899332545931e-07</v>
+        <v>2.810528502636411e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.677980420339736e-07</v>
+        <v>9.671787025780643e-13</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.788207666526432e-06</v>
+        <v>1.133546042946486e-13</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.924644134822302e-09</v>
+        <v>2.515068231803697e-13</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.363751941127703e-06</v>
+        <v>4.411780185967218e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.076035454796511e-06</v>
+        <v>3.206683779188174e-14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.552439698571106e-06</v>
+        <v>2.738680050969056e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>5.875233455299167e-06</v>
+        <v>5.299529261607039e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.617305083025713e-06</v>
+        <v>8.802816331768271e-13</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.068025529908482e-06</v>
+        <v>2.382926755223336e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.741987939065439e-06</v>
+        <v>7.308026254461419e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.097875605817535e-06</v>
+        <v>9.904398265078718e-14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.216160171679803e-06</v>
+        <v>5.089712221020663e-14</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.574686848471174e-06</v>
+        <v>2.263981103284296e-13</v>
       </c>
       <c r="AM6" t="n">
-        <v>7.494936653529294e-07</v>
+        <v>7.952694763575102e-14</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.62203093370772e-06</v>
+        <v>5.869838577872433e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.611307536426466e-06</v>
+        <v>9.147751187186387e-14</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.889363248774316e-07</v>
+        <v>3.885801253791961e-14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.961270982064889e-06</v>
+        <v>1.433904535906583e-13</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.218501205992652e-06</v>
+        <v>4.756065604284015e-14</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.307129289481963e-08</v>
+        <v>2.615715803677698e-13</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.326886831520824e-06</v>
+        <v>6.991483130283638e-14</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.524533884861739e-07</v>
+        <v>9.951705258470778e-13</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.563668754708488e-07</v>
+        <v>5.149055552593207e-13</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.347944817098323e-06</v>
+        <v>2.817979953117361e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.795202014269307e-06</v>
+        <v>6.154019351403694e-13</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.424562121130293e-06</v>
+        <v>1.381656833214506e-12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.547333214257378e-06</v>
+        <v>4.111877396732744e-13</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.443469606485451e-06</v>
+        <v>7.707681064575422e-13</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.914297394658206e-06</v>
+        <v>2.25445367669358e-13</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.816623236867599e-06</v>
+        <v>2.456194969635561e-13</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.726628503703978e-06</v>
+        <v>7.58119424442566e-13</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.704770617536269e-08</v>
+        <v>1.39517073566818e-13</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.829792826261837e-08</v>
+        <v>9.936132862667368e-13</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.005935807072092e-06</v>
+        <v>8.79788050137803e-13</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.276435447536642e-06</v>
+        <v>4.733854909629021e-13</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.113361577154137e-06</v>
+        <v>1.44526860097749e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.958236109407153e-07</v>
+        <v>1.233920517845766e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.594893541958299e-06</v>
+        <v>3.227122616442785e-13</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.672208777061314e-07</v>
+        <v>2.809377079929232e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.945422011180199e-06</v>
+        <v>8.678656209480662e-14</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.071762992272852e-06</v>
+        <v>1.13069811488991e-13</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.847652922355337e-06</v>
+        <v>2.835164557551256e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.016733676806325e-06</v>
+        <v>2.223364450448101e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.317184228355472e-07</v>
+        <v>9.626004962744183e-14</v>
       </c>
       <c r="BR6" t="n">
-        <v>3.513670890242793e-06</v>
+        <v>2.388805570453095e-13</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.339146463891666e-07</v>
+        <v>3.277764886767953e-13</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.568626081891125e-06</v>
+        <v>3.925930218938445e-13</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.116596649808343e-06</v>
+        <v>1.122174659510915e-13</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.661312686948804e-07</v>
+        <v>2.307656561499616e-15</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.818486111915263e-06</v>
+        <v>4.984524620312014e-14</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.913336063807947e-06</v>
+        <v>1.08637708204351e-12</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.015129434264963e-06</v>
+        <v>6.820473547920758e-13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.264092012817855e-07</v>
+        <v>6.670724085958146e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.373129862258793e-06</v>
+        <v>1.5274024720794e-13</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.660288035054691e-06</v>
+        <v>3.802529038171576e-13</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.295593278882734e-06</v>
+        <v>3.807603646439894e-13</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.796612707494205e-07</v>
+        <v>8.445564262044361e-14</v>
       </c>
       <c r="CE6" t="n">
-        <v>7.818389349267818e-07</v>
+        <v>2.089411407562788e-14</v>
       </c>
       <c r="CF6" t="n">
-        <v>6.230141593732696e-07</v>
+        <v>1.062743643087671e-13</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.119030571317126e-06</v>
+        <v>1.075453541867812e-13</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.086781082904054e-07</v>
+        <v>8.008323821792618e-15</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.859041276475182e-07</v>
+        <v>3.068128975707018e-13</v>
       </c>
       <c r="CJ6" t="n">
-        <v>6.09177220667334e-07</v>
+        <v>2.224853331081467e-13</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.702458914427552e-07</v>
+        <v>1.768790802302196e-14</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.0927395805993e-06</v>
+        <v>3.269323830754067e-13</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.243206947445287e-08</v>
+        <v>2.896997691650277e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.752297859842656e-06</v>
+        <v>6.563180988267137e-13</v>
       </c>
       <c r="CO6" t="n">
-        <v>3.010266880210111e-07</v>
+        <v>3.737240822799387e-13</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68719361681724e-06</v>
+        <v>9.204388553424314e-14</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.767187419929542e-06</v>
+        <v>9.433460956831397e-13</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.323393917118665e-06</v>
+        <v>1.250261016678272e-13</v>
       </c>
       <c r="CS6" t="n">
-        <v>6.525048092953512e-07</v>
+        <v>7.029178671416614e-13</v>
       </c>
       <c r="CT6" t="n">
-        <v>4.406516893595835e-07</v>
+        <v>5.873386629481891e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>6.547068096551811e-06</v>
+        <v>2.104291269228523e-13</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.183126983050897e-07</v>
+        <v>6.30740238142212e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.053362211678177e-06</v>
+        <v>1.500281019209404e-14</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.450274282888131e-07</v>
+        <v>1.082213745701166e-13</v>
       </c>
       <c r="CY6" t="n">
-        <v>9.849229627434397e-07</v>
+        <v>1.176117309011765e-13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.763189061421144e-07</v>
+        <v>2.324739521979841e-13</v>
       </c>
       <c r="DA6" t="n">
-        <v>6.422355909307953e-07</v>
+        <v>3.891451776701776e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.493958734499756e-07</v>
+        <v>2.472435233977222e-13</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.484412024410631e-07</v>
+        <v>4.277880607801536e-14</v>
       </c>
       <c r="DD6" t="n">
-        <v>7.393906003017037e-07</v>
+        <v>3.197272362229914e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.352392700937344e-06</v>
+        <v>7.341322645279535e-13</v>
       </c>
       <c r="DF6" t="n">
-        <v>3.608180122682825e-06</v>
+        <v>9.793716402098362e-13</v>
       </c>
       <c r="DG6" t="n">
-        <v>4.354554050678416e-07</v>
+        <v>6.322192660883352e-13</v>
       </c>
       <c r="DH6" t="n">
-        <v>3.586673528843676e-06</v>
+        <v>3.904729187556577e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>6.274387374105572e-07</v>
+        <v>4.579931811403426e-13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>7.263313364092028e-06</v>
+        <v>1.495223541335411e-12</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.480285274941707e-06</v>
+        <v>1.885844453687613e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>1.102192868529528e-06</v>
+        <v>3.429713110736365e-13</v>
       </c>
       <c r="DM6" t="n">
-        <v>4.184408226137748e-06</v>
+        <v>2.337091024179339e-13</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.197593178403622e-06</v>
+        <v>4.578006810446178e-13</v>
       </c>
       <c r="DO6" t="n">
-        <v>9.237518270310829e-07</v>
+        <v>3.768467200619685e-14</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.131053164106561e-09</v>
+        <v>1.243185919876447e-13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.004673436000303e-06</v>
+        <v>7.989389315052331e-13</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.202637112233788e-06</v>
+        <v>3.763774231516082e-13</v>
       </c>
       <c r="DS6" t="n">
-        <v>1.188765736515052e-06</v>
+        <v>9.799994339252868e-14</v>
       </c>
       <c r="DT6" t="n">
-        <v>2.834045744748437e-06</v>
+        <v>3.939754880839808e-13</v>
       </c>
       <c r="DU6" t="n">
-        <v>8.101201842691808e-08</v>
+        <v>4.343909129969625e-13</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.237738383177202e-06</v>
+        <v>1.648633080096953e-14</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.409007381880656e-06</v>
+        <v>1.865483678989421e-13</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.213975110658794e-06</v>
+        <v>5.163189212113728e-13</v>
       </c>
       <c r="DY6" t="n">
-        <v>4.395330392981123e-07</v>
+        <v>2.850387027103496e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.40905569626193e-06</v>
+        <v>6.244168051540433e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>2.203135863965144e-06</v>
+        <v>1.889222963182349e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>9.030119372255285e-07</v>
+        <v>3.618475961572609e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>7.194370255092508e-07</v>
+        <v>2.763860104323945e-13</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.497818743700918e-06</v>
+        <v>2.038228255878821e-13</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.089329998649191e-06</v>
+        <v>1.674291944236267e-13</v>
       </c>
       <c r="EF6" t="n">
-        <v>6.043682105882908e-07</v>
+        <v>1.240942570056303e-14</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.739081312734925e-06</v>
+        <v>1.340683477863563e-13</v>
       </c>
       <c r="EH6" t="n">
-        <v>2.199384425694006e-07</v>
+        <v>2.215700360816072e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>4.505470769800013e-06</v>
+        <v>3.774533853875828e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>9.685768418421503e-07</v>
+        <v>3.406517689458211e-13</v>
       </c>
       <c r="EK6" t="n">
-        <v>3.708584699779749e-06</v>
+        <v>2.539998647608371e-13</v>
       </c>
       <c r="EL6" t="n">
-        <v>3.020455778823816e-06</v>
+        <v>9.143735912203223e-15</v>
       </c>
       <c r="EM6" t="n">
-        <v>1.324461322838033e-06</v>
+        <v>7.111006933031155e-14</v>
       </c>
       <c r="EN6" t="n">
-        <v>6.692872034363972e-07</v>
+        <v>5.039084926238002e-13</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.35930326905509e-06</v>
+        <v>1.134831432384603e-13</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.208135699926061e-06</v>
+        <v>3.968979821449697e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>9.769838698048261e-07</v>
+        <v>1.486719818435955e-13</v>
       </c>
       <c r="ER6" t="n">
-        <v>1.414251187270565e-07</v>
+        <v>1.574954088586628e-13</v>
       </c>
       <c r="ES6" t="n">
-        <v>8.555326758141746e-08</v>
+        <v>7.326141646460393e-13</v>
       </c>
       <c r="ET6" t="n">
-        <v>1.627463234399329e-06</v>
+        <v>2.900640610949828e-13</v>
       </c>
       <c r="EU6" t="n">
-        <v>2.139508069376461e-06</v>
+        <v>3.387961027175035e-14</v>
       </c>
       <c r="EV6" t="n">
-        <v>5.043284545536153e-07</v>
+        <v>4.275178572699795e-14</v>
       </c>
       <c r="EW6" t="n">
-        <v>7.941997637317399e-07</v>
+        <v>6.012107044844894e-14</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.247196846383304e-07</v>
+        <v>8.335788114453846e-14</v>
       </c>
       <c r="EY6" t="n">
-        <v>8.648370339869871e-07</v>
+        <v>2.715836317770601e-14</v>
       </c>
       <c r="EZ6" t="n">
-        <v>5.254954658084898e-07</v>
+        <v>8.802968797698776e-14</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.665670879447134e-06</v>
+        <v>6.87854585573397e-14</v>
       </c>
       <c r="FB6" t="n">
-        <v>3.658752802948584e-07</v>
+        <v>1.201325551623139e-13</v>
       </c>
       <c r="FC6" t="n">
-        <v>1.773442619423804e-07</v>
+        <v>3.401700850256401e-13</v>
       </c>
       <c r="FD6" t="n">
-        <v>5.578727950705797e-07</v>
+        <v>2.388467028324737e-13</v>
       </c>
       <c r="FE6" t="n">
-        <v>4.242590989633754e-07</v>
+        <v>7.166088469151566e-15</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.415091557850246e-07</v>
+        <v>2.371824796027627e-13</v>
       </c>
       <c r="FG6" t="n">
-        <v>5.08170614921255e-07</v>
+        <v>5.983279735381763e-13</v>
       </c>
       <c r="FH6" t="n">
-        <v>1.47521484450408e-06</v>
+        <v>2.808772366167528e-13</v>
       </c>
       <c r="FI6" t="n">
-        <v>1.201898385261302e-06</v>
+        <v>2.527126186264994e-13</v>
       </c>
       <c r="FJ6" t="n">
-        <v>3.231282789784018e-06</v>
+        <v>7.389637404590921e-15</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.189958649978507e-06</v>
+        <v>1.429988397659565e-13</v>
       </c>
       <c r="FL6" t="n">
-        <v>1.954545723492629e-06</v>
+        <v>8.078590964591403e-14</v>
       </c>
       <c r="FM6" t="n">
-        <v>8.606688197687618e-07</v>
+        <v>1.107095643458622e-13</v>
       </c>
       <c r="FN6" t="n">
-        <v>1.137027993536321e-06</v>
+        <v>4.942130146963486e-13</v>
       </c>
       <c r="FO6" t="n">
-        <v>2.711178012759774e-06</v>
+        <v>6.040429658196733e-13</v>
       </c>
       <c r="FP6" t="n">
-        <v>2.462899374222616e-06</v>
+        <v>1.934325909083018e-13</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.48256185639184e-06</v>
+        <v>6.603595708448706e-13</v>
       </c>
       <c r="FR6" t="n">
-        <v>3.623362545113196e-06</v>
+        <v>8.690426850366251e-13</v>
       </c>
       <c r="FS6" t="n">
-        <v>3.297699322502012e-07</v>
+        <v>3.547584318322472e-13</v>
       </c>
       <c r="FT6" t="n">
-        <v>4.9022364692064e-06</v>
+        <v>2.492373982979773e-13</v>
       </c>
       <c r="FU6" t="n">
-        <v>6.526309334731195e-06</v>
+        <v>2.59106294362918e-13</v>
       </c>
       <c r="FV6" t="n">
-        <v>7.841019851184683e-07</v>
+        <v>8.74206956824608e-13</v>
       </c>
       <c r="FW6" t="n">
-        <v>2.822781652866979e-07</v>
+        <v>4.378304901790642e-13</v>
       </c>
       <c r="FX6" t="n">
-        <v>4.543827287761815e-07</v>
+        <v>3.651239738073492e-13</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.410278628100059e-06</v>
+        <v>7.234971898927717e-14</v>
       </c>
       <c r="FZ6" t="n">
-        <v>2.023879233092885e-06</v>
+        <v>1.762896469428843e-13</v>
       </c>
       <c r="GA6" t="n">
-        <v>3.099122068306315e-06</v>
+        <v>2.418644440543155e-13</v>
       </c>
       <c r="GB6" t="n">
-        <v>1.406039132234582e-06</v>
+        <v>2.029487689014786e-13</v>
       </c>
       <c r="GC6" t="n">
-        <v>1.535044361844484e-06</v>
+        <v>6.013563670463629e-13</v>
       </c>
       <c r="GD6" t="n">
-        <v>1.456953441447695e-06</v>
+        <v>7.797318563387834e-13</v>
       </c>
       <c r="GE6" t="n">
-        <v>5.563827926380327e-06</v>
+        <v>6.356984302022597e-14</v>
       </c>
       <c r="GF6" t="n">
-        <v>5.513395990419667e-06</v>
+        <v>4.740644725734211e-13</v>
       </c>
       <c r="GG6" t="n">
-        <v>6.281939477048581e-06</v>
+        <v>3.05466508207855e-13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.894118833474124e-10</v>
+        <v>3.684804665202714e-18</v>
       </c>
       <c r="B7" t="n">
-        <v>3.909277623836971e-10</v>
+        <v>5.573677797822147e-18</v>
       </c>
       <c r="C7" t="n">
-        <v>2.673969101696372e-10</v>
+        <v>2.189363116459632e-17</v>
       </c>
       <c r="D7" t="n">
-        <v>1.229676915848188e-10</v>
+        <v>1.907945849593374e-17</v>
       </c>
       <c r="E7" t="n">
-        <v>3.448420715645995e-10</v>
+        <v>5.942178075318089e-19</v>
       </c>
       <c r="F7" t="n">
-        <v>2.27923777074146e-10</v>
+        <v>3.112077464934369e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>8.025983766479783e-10</v>
+        <v>1.271111407389619e-17</v>
       </c>
       <c r="H7" t="n">
-        <v>2.065377036064575e-10</v>
+        <v>1.120078484577032e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>8.032813303415764e-11</v>
+        <v>2.555482354562341e-17</v>
       </c>
       <c r="J7" t="n">
-        <v>1.478691058487414e-10</v>
+        <v>3.630208263232376e-18</v>
       </c>
       <c r="K7" t="n">
-        <v>2.207245636265398e-10</v>
+        <v>2.942429338744644e-17</v>
       </c>
       <c r="L7" t="n">
-        <v>3.270727022552933e-10</v>
+        <v>2.065545428416775e-17</v>
       </c>
       <c r="M7" t="n">
-        <v>2.455141090429436e-10</v>
+        <v>3.509505985530577e-17</v>
       </c>
       <c r="N7" t="n">
-        <v>1.431606166946153e-09</v>
+        <v>7.303643330915549e-18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.142788641494974e-10</v>
+        <v>2.461618365425131e-17</v>
       </c>
       <c r="P7" t="n">
-        <v>3.416106841847011e-10</v>
+        <v>2.040012348140733e-17</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.810213058569772e-11</v>
+        <v>2.348893169396609e-17</v>
       </c>
       <c r="R7" t="n">
-        <v>2.96400071153613e-10</v>
+        <v>1.363819494338847e-17</v>
       </c>
       <c r="S7" t="n">
-        <v>9.839784542720054e-11</v>
+        <v>6.78905427184631e-18</v>
       </c>
       <c r="T7" t="n">
-        <v>4.577331569333154e-11</v>
+        <v>2.19587997619757e-17</v>
       </c>
       <c r="U7" t="n">
-        <v>9.011619922505432e-11</v>
+        <v>5.943580146456366e-18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.309680142114189e-10</v>
+        <v>2.287152408475651e-17</v>
       </c>
       <c r="W7" t="n">
-        <v>3.631754896815664e-10</v>
+        <v>3.543881626554811e-17</v>
       </c>
       <c r="X7" t="n">
-        <v>3.992136066166552e-10</v>
+        <v>1.799583204115458e-17</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.501071766885076e-10</v>
+        <v>1.120268322527613e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.019151013581521e-10</v>
+        <v>1.494038402270008e-17</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.164135702922067e-11</v>
+        <v>5.66757892736886e-18</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.885332499122597e-11</v>
+        <v>8.791371503164634e-18</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.096350094043075e-11</v>
+        <v>8.447171724113969e-18</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.256897251890933e-10</v>
+        <v>1.338331081815883e-17</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.394095170530022e-10</v>
+        <v>1.551193108438849e-17</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.431555512494299e-10</v>
+        <v>2.091712294478155e-20</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.20051477040073e-10</v>
+        <v>1.684023094691594e-17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.052075232488292e-10</v>
+        <v>2.915128614858607e-18</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.206747284905219e-10</v>
+        <v>1.94438083947062e-17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.708280544272412e-10</v>
+        <v>5.29151863266449e-18</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.483640459434056e-11</v>
+        <v>1.050496216885194e-17</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.958550237077475e-11</v>
+        <v>1.10466686899425e-17</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.318303105568575e-12</v>
+        <v>4.818652563692426e-18</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.38881053826745e-10</v>
+        <v>1.953333746112526e-17</v>
       </c>
       <c r="AO7" t="n">
-        <v>4.67930805214678e-10</v>
+        <v>1.479248082045314e-17</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.522105078232698e-11</v>
+        <v>1.400092729047308e-18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.208236843908139e-10</v>
+        <v>7.01574725461953e-18</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.126565312732254e-10</v>
+        <v>1.249617532762735e-17</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.872005576750382e-12</v>
+        <v>1.033336024205536e-17</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.100684265953333e-10</v>
+        <v>4.399604106143981e-19</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.106229328255552e-10</v>
+        <v>4.660843460019865e-17</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.156366599697201e-10</v>
+        <v>2.580026788570259e-18</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.0385587075682e-11</v>
+        <v>6.787684874342229e-18</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.158963702258987e-10</v>
+        <v>1.212959452274284e-17</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.19721837946274e-10</v>
+        <v>8.985270083372577e-19</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.19526929757086e-11</v>
+        <v>3.30162813568855e-18</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.773127283361987e-10</v>
+        <v>1.301786407789413e-17</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.778004020738024e-10</v>
+        <v>1.088865651342956e-17</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.076864847293635e-10</v>
+        <v>1.308549932786014e-17</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.635693108736902e-10</v>
+        <v>2.188827434294943e-17</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.517250852207553e-10</v>
+        <v>1.163905367203205e-18</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.518757755813454e-12</v>
+        <v>1.69300693788841e-17</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.085014188553004e-10</v>
+        <v>2.630120432876164e-18</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.645145710417523e-11</v>
+        <v>1.455076706493657e-17</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.724568041820532e-11</v>
+        <v>1.222690735872602e-17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.240056612423658e-10</v>
+        <v>7.619249544141787e-19</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6052389679474e-10</v>
+        <v>6.118537117817457e-18</v>
       </c>
       <c r="BL7" t="n">
-        <v>9.809206225064315e-11</v>
+        <v>1.380295856806107e-17</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.578379259572273e-10</v>
+        <v>1.540780062579664e-17</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.913416994292483e-11</v>
+        <v>3.019314494551498e-18</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.208554367693182e-10</v>
+        <v>2.55510673184618e-18</v>
       </c>
       <c r="BP7" t="n">
-        <v>8.248483007733398e-10</v>
+        <v>1.977069197481368e-17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.43766098920284e-10</v>
+        <v>1.486512547620878e-17</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.53964932417361e-10</v>
+        <v>1.687780645342178e-17</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.076470467267001e-10</v>
+        <v>3.685890753346996e-18</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.412786968112982e-12</v>
+        <v>2.263605802440656e-18</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.893951827649289e-11</v>
+        <v>1.619220111142965e-18</v>
       </c>
       <c r="BV7" t="n">
-        <v>2.382989083837828e-10</v>
+        <v>4.178424695743733e-18</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.639404915269708e-11</v>
+        <v>1.07819163000051e-17</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.667687793416306e-10</v>
+        <v>2.079582187103432e-17</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.921790280360995e-10</v>
+        <v>1.740547158361425e-17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.461363530186333e-10</v>
+        <v>2.226548855460831e-17</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.19323800840121e-10</v>
+        <v>3.416185412696784e-18</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.120019355038693e-10</v>
+        <v>1.349916325321117e-17</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.686005501877474e-10</v>
+        <v>1.604616899172831e-17</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.823536791682571e-11</v>
+        <v>3.841244784961499e-18</v>
       </c>
       <c r="CE7" t="n">
-        <v>6.605057473185738e-11</v>
+        <v>1.002390494386407e-18</v>
       </c>
       <c r="CF7" t="n">
-        <v>4.400981662433523e-11</v>
+        <v>4.29702212965883e-18</v>
       </c>
       <c r="CG7" t="n">
-        <v>6.344248737466529e-11</v>
+        <v>9.86108147131821e-18</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.539175979534349e-11</v>
+        <v>2.761630362948367e-18</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.072088667841697e-10</v>
+        <v>5.581423517078093e-18</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.335742350061508e-10</v>
+        <v>2.367123526993757e-18</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.769575442404751e-11</v>
+        <v>2.803124017220711e-18</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.170697011554367e-10</v>
+        <v>7.736101626964397e-18</v>
       </c>
       <c r="CM7" t="n">
-        <v>8.015640234892984e-11</v>
+        <v>1.24822846903959e-18</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.562764223583812e-10</v>
+        <v>1.319299475718386e-17</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.288420481415642e-10</v>
+        <v>1.137027249892121e-17</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.272437710753138e-10</v>
+        <v>1.304848547699023e-17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.950991950800841e-10</v>
+        <v>8.653277008621357e-18</v>
       </c>
       <c r="CR7" t="n">
-        <v>2.59872678931572e-12</v>
+        <v>1.934459883357843e-18</v>
       </c>
       <c r="CS7" t="n">
-        <v>4.44503378549399e-10</v>
+        <v>5.292694056314927e-18</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.350347221875438e-10</v>
+        <v>7.873726282919745e-18</v>
       </c>
       <c r="CU7" t="n">
-        <v>2.226972217744816e-10</v>
+        <v>1.322186418774257e-17</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.427567868945602e-11</v>
+        <v>5.852050543725842e-18</v>
       </c>
       <c r="CW7" t="n">
-        <v>6.163006910364643e-11</v>
+        <v>2.069062796836746e-19</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.774276294803535e-11</v>
+        <v>2.587833719191535e-18</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.220366863119438e-11</v>
+        <v>9.88342775556633e-18</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.01520779230524e-11</v>
+        <v>2.926463057202115e-18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.074076938500923e-10</v>
+        <v>4.628999487978412e-18</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.725452419831797e-10</v>
+        <v>9.152281984950096e-19</v>
       </c>
       <c r="DC7" t="n">
-        <v>5.588271512202425e-11</v>
+        <v>1.422855085143542e-18</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.888226463548804e-11</v>
+        <v>6.459713965319547e-18</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.127477499724861e-10</v>
+        <v>2.480815986671568e-18</v>
       </c>
       <c r="DF7" t="n">
-        <v>7.092542109177202e-10</v>
+        <v>1.363364462283882e-17</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.315116709450393e-10</v>
+        <v>4.732579457872608e-19</v>
       </c>
       <c r="DH7" t="n">
-        <v>7.2454520161358e-10</v>
+        <v>1.720680265281372e-17</v>
       </c>
       <c r="DI7" t="n">
-        <v>6.152553466698407e-10</v>
+        <v>4.635312530413416e-18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.134261266663941e-10</v>
+        <v>1.234565906182536e-17</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.64614402506669e-10</v>
+        <v>2.603656857129061e-18</v>
       </c>
       <c r="DL7" t="n">
-        <v>3.935834158586005e-10</v>
+        <v>1.371383254539547e-18</v>
       </c>
       <c r="DM7" t="n">
-        <v>1.302245256074031e-10</v>
+        <v>5.249377916357976e-18</v>
       </c>
       <c r="DN7" t="n">
-        <v>4.937194750254115e-12</v>
+        <v>1.78201049646432e-18</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.948120831318789e-10</v>
+        <v>3.689403789408509e-18</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.347312507346217e-11</v>
+        <v>4.986343994143157e-19</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.000826310188941e-10</v>
+        <v>2.040365388826171e-17</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.86468243623672e-10</v>
+        <v>1.148917681684356e-18</v>
       </c>
       <c r="DS7" t="n">
-        <v>4.763885813607871e-11</v>
+        <v>1.273997275110694e-17</v>
       </c>
       <c r="DT7" t="n">
-        <v>2.951948130380799e-10</v>
+        <v>1.440576395791725e-17</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.409289629439314e-10</v>
+        <v>6.14108916324295e-19</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.023939779134288e-11</v>
+        <v>6.159454433998005e-18</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.241092034171999e-11</v>
+        <v>1.094168540813911e-17</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.403266391974967e-10</v>
+        <v>4.497033988183845e-18</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.653333719930927e-10</v>
+        <v>7.444251213750069e-19</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.344025724048237e-10</v>
+        <v>1.273022277322678e-18</v>
       </c>
       <c r="EA7" t="n">
-        <v>3.792296338067658e-11</v>
+        <v>1.240338468805299e-17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.407496064143032e-10</v>
+        <v>1.743906835137371e-18</v>
       </c>
       <c r="EC7" t="n">
-        <v>5.246361331479044e-11</v>
+        <v>8.37091559780393e-18</v>
       </c>
       <c r="ED7" t="n">
-        <v>3.194949582674411e-10</v>
+        <v>5.866141151870377e-18</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.187550613401811e-10</v>
+        <v>1.232743379138898e-17</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.478304111068862e-11</v>
+        <v>2.404287304349693e-18</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.62578381313061e-10</v>
+        <v>5.934079563530888e-18</v>
       </c>
       <c r="EH7" t="n">
-        <v>6.984775258178644e-11</v>
+        <v>6.859443619661816e-18</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.242339508518043e-10</v>
+        <v>1.555384928911023e-17</v>
       </c>
       <c r="EJ7" t="n">
-        <v>2.393871906258838e-11</v>
+        <v>5.789681125539344e-18</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.104777047096107e-10</v>
+        <v>1.519410068589267e-19</v>
       </c>
       <c r="EL7" t="n">
-        <v>2.022201329998641e-11</v>
+        <v>2.508314778955281e-18</v>
       </c>
       <c r="EM7" t="n">
-        <v>7.435130983113325e-11</v>
+        <v>2.090057933253049e-18</v>
       </c>
       <c r="EN7" t="n">
-        <v>4.201773651235641e-11</v>
+        <v>1.077648916800614e-17</v>
       </c>
       <c r="EO7" t="n">
-        <v>7.093228782117933e-11</v>
+        <v>6.718044538571389e-18</v>
       </c>
       <c r="EP7" t="n">
-        <v>7.026772913532042e-11</v>
+        <v>1.853655669885804e-17</v>
       </c>
       <c r="EQ7" t="n">
-        <v>7.978560173649285e-11</v>
+        <v>1.618150566610934e-17</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.831641587874856e-10</v>
+        <v>3.425117929336591e-18</v>
       </c>
       <c r="ES7" t="n">
-        <v>2.718365810228107e-11</v>
+        <v>6.653498394602958e-18</v>
       </c>
       <c r="ET7" t="n">
-        <v>4.269211373308934e-11</v>
+        <v>1.648339515682792e-17</v>
       </c>
       <c r="EU7" t="n">
-        <v>3.931439548909843e-11</v>
+        <v>1.097203301045245e-17</v>
       </c>
       <c r="EV7" t="n">
-        <v>9.989151172895561e-11</v>
+        <v>3.393806661609621e-18</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.536235305632516e-10</v>
+        <v>6.799980500557523e-18</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.076958396934891e-11</v>
+        <v>7.57669151521624e-18</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.795421797345931e-11</v>
+        <v>1.389423029723563e-18</v>
       </c>
       <c r="EZ7" t="n">
-        <v>2.632450507578099e-11</v>
+        <v>5.585722788311838e-18</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.590733877427809e-11</v>
+        <v>1.120413244570932e-17</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.223105810024052e-11</v>
+        <v>2.674675482595567e-18</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.969197027662517e-10</v>
+        <v>7.18826735189604e-18</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.705168645171895e-10</v>
+        <v>3.830044759467531e-18</v>
       </c>
       <c r="FE7" t="n">
-        <v>7.374875710119966e-11</v>
+        <v>2.535567071416453e-18</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.489142142929722e-11</v>
+        <v>7.784169092359854e-18</v>
       </c>
       <c r="FG7" t="n">
-        <v>9.936109227060008e-12</v>
+        <v>2.422784717207604e-17</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.584528758202808e-10</v>
+        <v>4.150864692094691e-18</v>
       </c>
       <c r="FI7" t="n">
-        <v>9.1728173667871e-11</v>
+        <v>9.786189365838271e-18</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.354108075668492e-10</v>
+        <v>6.875002886983939e-18</v>
       </c>
       <c r="FK7" t="n">
-        <v>2.710690005791605e-11</v>
+        <v>4.480652916923152e-18</v>
       </c>
       <c r="FL7" t="n">
-        <v>6.044348355160878e-11</v>
+        <v>7.739500512101377e-18</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.428719087481767e-10</v>
+        <v>9.593807834873751e-18</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.290668683040508e-10</v>
+        <v>9.209901318469009e-19</v>
       </c>
       <c r="FO7" t="n">
-        <v>2.802590937101002e-10</v>
+        <v>1.046869526207516e-17</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.544217614364186e-10</v>
+        <v>2.567363480572685e-18</v>
       </c>
       <c r="FQ7" t="n">
-        <v>5.565958804965021e-10</v>
+        <v>4.710785316683367e-19</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.891924117369825e-10</v>
+        <v>4.587754608275293e-18</v>
       </c>
       <c r="FS7" t="n">
-        <v>6.835385035763863e-11</v>
+        <v>1.283006595470377e-17</v>
       </c>
       <c r="FT7" t="n">
-        <v>1.664809540224965e-10</v>
+        <v>2.083625942245959e-17</v>
       </c>
       <c r="FU7" t="n">
-        <v>2.817075184236018e-10</v>
+        <v>9.744709566841187e-18</v>
       </c>
       <c r="FV7" t="n">
-        <v>1.207089983523701e-11</v>
+        <v>2.215785746766414e-17</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.534434385108696e-10</v>
+        <v>1.130691790862516e-19</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.889939676453679e-11</v>
+        <v>6.783857923238252e-18</v>
       </c>
       <c r="FY7" t="n">
-        <v>7.007880387099874e-12</v>
+        <v>5.150935565248346e-18</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.569811086676864e-10</v>
+        <v>6.059891666748672e-18</v>
       </c>
       <c r="GA7" t="n">
-        <v>4.213184523482738e-10</v>
+        <v>2.932112907581005e-18</v>
       </c>
       <c r="GB7" t="n">
-        <v>6.497949400774417e-11</v>
+        <v>7.589891663431362e-18</v>
       </c>
       <c r="GC7" t="n">
-        <v>3.391952274611754e-10</v>
+        <v>5.353234991757377e-18</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.257967312071287e-10</v>
+        <v>9.515222367958763e-18</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.549992079130647e-10</v>
+        <v>3.851970008783861e-18</v>
       </c>
       <c r="GF7" t="n">
-        <v>5.127947372285391e-11</v>
+        <v>3.390689017880909e-18</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.937400101459374e-10</v>
+        <v>8.971389992693937e-18</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0007912904256954789</v>
+        <v>0.001099447603337467</v>
       </c>
       <c r="B9" t="n">
-        <v>0.006963213440030813</v>
+        <v>0.00405962485820055</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008649448282085359</v>
+        <v>0.0001544211991131306</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003683819668367505</v>
+        <v>0.004412272479385138</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001732517499476671</v>
+        <v>8.563746814616024e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00165660516358912</v>
+        <v>0.005610428284853697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004042154178023338</v>
+        <v>0.003604705911129713</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0007118902867659926</v>
+        <v>0.003763209795579314</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001016485970467329</v>
+        <v>0.0001983007969101891</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00140765868127346</v>
+        <v>0.001186726382002234</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005162277724593878</v>
+        <v>0.004372210241854191</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001560529053676873</v>
+        <v>0.001182181993499398</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003368377918377519</v>
+        <v>0.007562479469925165</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002069295383989811</v>
+        <v>0.002226128475740552</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002773453248664737</v>
+        <v>0.006852434016764164</v>
       </c>
       <c r="P9" t="n">
-        <v>1.959878136403859e-05</v>
+        <v>0.003923420794308186</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000329194706864655</v>
+        <v>0.0003590960404835641</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001218141638673842</v>
+        <v>0.0007882887730374932</v>
       </c>
       <c r="S9" t="n">
-        <v>9.199338092003018e-05</v>
+        <v>0.0003808709152508527</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004303591558709741</v>
+        <v>0.0001730300864437595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0003888037463184446</v>
+        <v>0.001082499045878649</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001216477015987039</v>
+        <v>0.00106118933763355</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00159093807451427</v>
+        <v>0.001995917176827788</v>
       </c>
       <c r="X9" t="n">
-        <v>6.437234696932137e-05</v>
+        <v>0.002274336293339729</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0007017864845693111</v>
+        <v>6.69296714477241e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0004557601059786975</v>
+        <v>0.001216110889799893</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0006773834466002882</v>
+        <v>0.001086195465177298</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000133630441268906</v>
+        <v>0.0015887466724962</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00130923290271312</v>
+        <v>0.001626581884920597</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.000287766830297187</v>
+        <v>0.001104825409129262</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.000229055032832548</v>
+        <v>0.0007134932093322277</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0008753067813813686</v>
+        <v>0.001446236274205148</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0005692457780241966</v>
+        <v>0.002576522994786501</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001460396451875567</v>
+        <v>0.0005491729825735092</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.057517147273757e-05</v>
+        <v>0.00290969479829073</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0003335698565933853</v>
+        <v>0.001263994257897139</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0004808729281648993</v>
+        <v>0.0005280331242829561</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0006541645270772278</v>
+        <v>0.001534402021206915</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.858032091055065e-05</v>
+        <v>0.001780506339855492</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001763394539011642</v>
+        <v>0.001786941662430763</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001073815277777612</v>
+        <v>0.0001074493629857898</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0009300487581640482</v>
+        <v>0.00138421927113086</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001462416548747569</v>
+        <v>0.0008215740672312677</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.00011004030238837</v>
+        <v>0.001275202841497958</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0006126280641183257</v>
+        <v>0.000845214759465307</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.220309296622872e-05</v>
+        <v>0.0001537208445370197</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00438349274918437</v>
+        <v>0.004685355350375175</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.375637217890471e-06</v>
+        <v>0.002008213195949793</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001173520111478865</v>
+        <v>0.002944424981251359</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0007980277296155691</v>
+        <v>0.004893326200544834</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0008169611101038754</v>
+        <v>0.00434098532423377</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0009379962575621903</v>
+        <v>0.0004140780074521899</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0008246222278103232</v>
+        <v>0.0004354330594651401</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0003509781090542674</v>
+        <v>1.437359605915844e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001690774952294305</v>
+        <v>0.001428018091246486</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001774443895556033</v>
+        <v>0.0005809958092868328</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001548528671264648</v>
+        <v>0.0005001240642741323</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0005057164817117155</v>
+        <v>0.001684191985987127</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001550997723825276</v>
+        <v>0.002995248883962631</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001221064245328307</v>
+        <v>0.0004655570955947042</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0007560009253211319</v>
+        <v>0.0005606628837995231</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003259979421272874</v>
+        <v>0.002701695309951901</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0008405468543060124</v>
+        <v>0.0003809919871855527</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0004395539290271699</v>
+        <v>0.0004671488713938743</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0008786273538134992</v>
+        <v>0.001858807634562254</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0006074109114706516</v>
+        <v>0.0004282601294107735</v>
       </c>
       <c r="BO9" t="n">
-        <v>6.034522084519267e-05</v>
+        <v>0.0007277829572558403</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0007179794483818114</v>
+        <v>0.0003455992264207453</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0007068333216011524</v>
+        <v>0.0004920496721751988</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0001245737366843969</v>
+        <v>0.002161845099180937</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.000138093950226903</v>
+        <v>0.0006109259556978941</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0002907018351834267</v>
+        <v>0.0009872341761365533</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001774240809027106</v>
+        <v>2.441675314912573e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002180635463446379</v>
+        <v>0.002634947188198566</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0005234594573266804</v>
+        <v>0.001188432332128286</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001190810231491923</v>
+        <v>0.004408973269164562</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0004161761025898159</v>
+        <v>0.001733613898977637</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0004607433802448213</v>
+        <v>0.002716324990615249</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0002122403238900006</v>
+        <v>0.0004824080970138311</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0005980860441923141</v>
+        <v>0.0001475275494158268</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0008152886875905097</v>
+        <v>0.00132430880330503</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0002489591133780777</v>
+        <v>0.0003526193322613835</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00116163631901145</v>
+        <v>0.001442444860003889</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0004660101549234241</v>
+        <v>0.0003505111671984196</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0004415094444993883</v>
+        <v>0.001644380390644073</v>
       </c>
       <c r="CH9" t="n">
-        <v>4.166192229604349e-05</v>
+        <v>9.912673704093322e-06</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0003460060397628695</v>
+        <v>0.0007961704395711422</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001468524424126372</v>
+        <v>0.0008278118912130594</v>
       </c>
       <c r="CK9" t="n">
-        <v>6.529634993057698e-05</v>
+        <v>0.0008139068959280849</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0001195626828121021</v>
+        <v>0.0001961178058991209</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0007414098945446312</v>
+        <v>0.000784281874075532</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.000378573196940124</v>
+        <v>0.001572053995914757</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0004788295191247016</v>
+        <v>0.003104269271716475</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0007155988132581115</v>
+        <v>0.003859974211081862</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.121757228858769e-05</v>
+        <v>0.0001100687368307263</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0001349192461930215</v>
+        <v>0.0001120674423873425</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001025055418722332</v>
+        <v>0.001020813127979636</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001110141747631133</v>
+        <v>0.001750920666381717</v>
       </c>
       <c r="CU9" t="n">
-        <v>8.65693436935544e-07</v>
+        <v>0.000562404515221715</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002375656040385365</v>
+        <v>0.0004262047878000885</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.00094188580987975</v>
+        <v>0.001216945238411427</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005911737098358572</v>
+        <v>4.950747825205326e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0006227815174497664</v>
+        <v>0.002025860361754894</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001276016992051154</v>
+        <v>0.0005436877836473286</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0002786602708511055</v>
+        <v>0.0008822562522254884</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001787889195838943</v>
+        <v>0.0007015354931354523</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0001506995467934757</v>
+        <v>0.0006774046923965216</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001454232988180593</v>
+        <v>0.0003348789177834988</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00062999950023368</v>
+        <v>0.000243190283072181</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0005299545009620488</v>
+        <v>9.224517270922661e-06</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.000605075154453516</v>
+        <v>0.001622182782739401</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002537080319598317</v>
+        <v>0.000584035471547395</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.00167538842651993</v>
+        <v>0.0007165963761508465</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0005703526549041271</v>
+        <v>0.002461949363350868</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0007745783659629524</v>
+        <v>0.0001096942869480699</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007518348284065723</v>
+        <v>0.00488775409758091</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0002008741139434278</v>
+        <v>0.001487319823354483</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0006092935218475759</v>
+        <v>0.0004623074783012271</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0005091142957098782</v>
+        <v>0.001047730562277138</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0003804017324000597</v>
+        <v>6.490212399512529e-06</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004128241562284529</v>
+        <v>0.0002981774159707129</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0004882831708528101</v>
+        <v>0.0008741525816731155</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.000491100421641022</v>
+        <v>0.0001046956167556345</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003163405926898122</v>
+        <v>0.0007202500710263848</v>
       </c>
       <c r="DU9" t="n">
-        <v>7.974135951371863e-05</v>
+        <v>0.001589488936588168</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0004949257127009332</v>
+        <v>0.002168646547943354</v>
       </c>
       <c r="DW9" t="n">
-        <v>5.699809116777033e-05</v>
+        <v>0.0001449606061214581</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002490959304850549</v>
+        <v>0.0001008963590720668</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0008013571496121585</v>
+        <v>0.001534278271719813</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.700551365502179e-06</v>
+        <v>0.001673645572736859</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.000281776039628312</v>
+        <v>0.0003857683332171291</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0002533782972022891</v>
+        <v>0.001795542775653303</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.00016156212950591</v>
+        <v>0.001223562401719391</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0003093742416240275</v>
+        <v>0.002584690228104591</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001593028282513842</v>
+        <v>0.003021853510290384</v>
       </c>
       <c r="EF9" t="n">
-        <v>5.106967000756413e-05</v>
+        <v>0.001199606107547879</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0008447696454823017</v>
+        <v>0.0003845164028462023</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001951083249878138</v>
+        <v>0.001460168277844787</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0003508071531541646</v>
+        <v>0.00154771888628602</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0006126294028945267</v>
+        <v>9.827969188336283e-05</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001238839904544875</v>
+        <v>0.0003106247750110924</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0002022194094024599</v>
+        <v>0.000234008562983945</v>
       </c>
       <c r="EM9" t="n">
-        <v>5.490868716151454e-05</v>
+        <v>0.0002399455552222207</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.381079997983761e-05</v>
+        <v>0.0002374675386818126</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0003351586638018489</v>
+        <v>0.0003954932035412639</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0008054833742789924</v>
+        <v>0.001510734902694821</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.000286302762106061</v>
+        <v>7.743964670225978e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0005517832469195127</v>
+        <v>0.00119364564307034</v>
       </c>
       <c r="ES9" t="n">
-        <v>4.038011320517398e-05</v>
+        <v>3.520525206113234e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001455732621252537</v>
+        <v>0.0001314069086220115</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0007020377088338137</v>
+        <v>0.001118804328143597</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006936300196684897</v>
+        <v>0.0005011491593904793</v>
       </c>
       <c r="EW9" t="n">
-        <v>9.392884385306388e-05</v>
+        <v>0.002430440858006477</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0001494041061960161</v>
+        <v>0.0004274286911822855</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0008606088231317699</v>
+        <v>0.001502509927377105</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0003199341299477965</v>
+        <v>0.0002075615921057761</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0005897662485949695</v>
+        <v>0.00224254047498107</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0001491055736551061</v>
+        <v>9.252227755496278e-06</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0004453093861229718</v>
+        <v>0.0008758272742852569</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0002974506351165473</v>
+        <v>0.001163439941592515</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001434595178579912</v>
+        <v>0.0009784594876691699</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.000290204567136243</v>
+        <v>0.000201265444047749</v>
       </c>
       <c r="FG9" t="n">
-        <v>9.993774438044056e-05</v>
+        <v>5.881933611817658e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002034336066571996</v>
+        <v>0.0009616772877052426</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001454087614547461</v>
+        <v>0.0008686088258400559</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003799024561885744</v>
+        <v>0.001465487526729703</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001173286364064552</v>
+        <v>0.000631756498478353</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0001357110886601731</v>
+        <v>0.0003227212582714856</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.442196662537754e-05</v>
+        <v>0.0005344470264390111</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0003640326322056353</v>
+        <v>0.001557436306029558</v>
       </c>
       <c r="FO9" t="n">
-        <v>5.267962842481211e-05</v>
+        <v>0.002011099830269814</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0007823668420314789</v>
+        <v>0.002018706407397985</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001828325039241463</v>
+        <v>0.00292781600728631</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0004622621927410364</v>
+        <v>0.003069743514060974</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0004167331499047577</v>
+        <v>0.003254851792007685</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.000271379976766184</v>
+        <v>0.002058230340480804</v>
       </c>
       <c r="FU9" t="n">
-        <v>5.161878652870655e-05</v>
+        <v>0.001680206740275025</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0006770299514755607</v>
+        <v>7.708324119448662e-06</v>
       </c>
       <c r="FW9" t="n">
-        <v>6.617780309170485e-05</v>
+        <v>0.005438864696770906</v>
       </c>
       <c r="FX9" t="n">
-        <v>1.757531572366133e-05</v>
+        <v>2.546578616602346e-05</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0005224694032222033</v>
+        <v>9.349497850053012e-05</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0003418028936721385</v>
+        <v>0.001527412096038461</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.000371541187632829</v>
+        <v>0.0008541945135220885</v>
       </c>
       <c r="GB9" t="n">
-        <v>8.37270199554041e-05</v>
+        <v>0.002276561222970486</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0005261267069727182</v>
+        <v>0.001168135553598404</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0006142852362245321</v>
+        <v>0.001908833626657724</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.00182050745934248</v>
+        <v>0.002123364713042974</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0003856857365462929</v>
+        <v>0.0008882301626726985</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0002760966308414936</v>
+        <v>0.0008759742486290634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.01019407715648413</v>
+        <v>0.005153501871973276</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1801637262105942</v>
+        <v>0.01570358127355576</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006336026126518846</v>
+        <v>0.00269851298071444</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1062863320112228</v>
+        <v>0.02584477327764034</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01544757932424545</v>
+        <v>0.003121231449767947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04674230515956879</v>
+        <v>0.009289184585213661</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02505025640130043</v>
+        <v>0.01657765731215477</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01818341761827469</v>
+        <v>0.01200357172638178</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004241243004798889</v>
+        <v>0.007377267349511385</v>
       </c>
       <c r="J10" t="n">
-        <v>0.007854130119085312</v>
+        <v>0.009538363665342331</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07733249664306641</v>
+        <v>0.009559202939271927</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02063116990029812</v>
+        <v>0.002583206165581942</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1468565464019775</v>
+        <v>0.03569712862372398</v>
       </c>
       <c r="N10" t="n">
-        <v>0.106792613863945</v>
+        <v>0.01123756263405085</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08210784941911697</v>
+        <v>0.00258282758295536</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03123126737773418</v>
+        <v>0.01736454851925373</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.002932848175987601</v>
+        <v>0.0002469208557158709</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005218027625232935</v>
+        <v>0.006664929445832968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00140341988299042</v>
+        <v>0.001907279947772622</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04772871360182762</v>
+        <v>0.007010097149759531</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03315438330173492</v>
+        <v>0.001416868763044477</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0292340163141489</v>
+        <v>0.0005829519359394908</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009650253690779209</v>
+        <v>0.0007570266025140882</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03090397454798222</v>
+        <v>0.003572750836610794</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.008141896687448025</v>
+        <v>0.001036814646795392</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001441766507923603</v>
+        <v>0.01071271114051342</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01228813827037811</v>
+        <v>0.001969286939129233</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03364168107509613</v>
+        <v>0.000445365032646805</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03275560587644577</v>
+        <v>0.005959279369562864</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006387217901647091</v>
+        <v>0.001090411213226616</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.02958798408508301</v>
+        <v>0.0004625217407010496</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.008786726742982864</v>
+        <v>0.002359105739742517</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.005633050110191107</v>
+        <v>0.005766021087765694</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01376510504633188</v>
+        <v>0.0003727323492057621</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.002543817274272442</v>
+        <v>0.009703009389340878</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.006050571799278259</v>
+        <v>0.001903977477923036</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02241778559982777</v>
+        <v>0.001220646779984236</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.008348365314304829</v>
+        <v>0.005693392362445593</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01936288923025131</v>
+        <v>0.002643804298713803</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02748372033238411</v>
+        <v>0.000273505924269557</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02720941975712776</v>
+        <v>0.002362653613090515</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0303780697286129</v>
+        <v>0.003385432763025165</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.003923144191503525</v>
+        <v>0.006615492515265942</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01755867712199688</v>
+        <v>0.002564616268500686</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.003653600811958313</v>
+        <v>0.0008361390791833401</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01668516360223293</v>
+        <v>0.001895542489364743</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2009805738925934</v>
+        <v>0.001287028193473816</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.04216155037283897</v>
+        <v>0.001840236596763134</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003091036109253764</v>
+        <v>0.006456532049924135</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.07702149450778961</v>
+        <v>0.02270234562456608</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.04171834141016006</v>
+        <v>0.001207886496558785</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002853477373719215</v>
+        <v>0.000629755319096148</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.02557119354605675</v>
+        <v>0.003393424907699227</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0175375584512949</v>
+        <v>0.001728404778987169</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.02830028906464577</v>
+        <v>0.007102484814822674</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006032869219779968</v>
+        <v>0.005025168415158987</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03336466103792191</v>
+        <v>0.00241208984516561</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.04160056263208389</v>
+        <v>0.005445647053420544</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.08334789425134659</v>
+        <v>0.01349959243088961</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.05970383062958717</v>
+        <v>0.004427330568432808</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.02529714442789555</v>
+        <v>0.003364324569702148</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.002700528129935265</v>
+        <v>0.02134116552770138</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.007785032968968153</v>
+        <v>0.001150435069575906</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.07705506682395935</v>
+        <v>0.0002727939863689244</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07349700480699539</v>
+        <v>0.003746537491679192</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.003695690538734198</v>
+        <v>0.001988652627915144</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.03780749440193176</v>
+        <v>0.005643176380544901</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.06976926326751709</v>
+        <v>0.00572478910908103</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02539201453328133</v>
+        <v>0.004256477113813162</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.008808056823909283</v>
+        <v>0.00141764641739428</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.00505965668708086</v>
+        <v>0.003404867369681597</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.01203387975692749</v>
+        <v>0.003774588461965322</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01443396229296923</v>
+        <v>0.002279856707900763</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.09648457914590836</v>
+        <v>0.004559851251542568</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.006839264649897814</v>
+        <v>0.0009293328039348125</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01490160170942545</v>
+        <v>0.01096039824187756</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.006327751092612743</v>
+        <v>0.007066832389682531</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.07062406837940216</v>
+        <v>0.003126654541119933</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.00367334857583046</v>
+        <v>0.002165367128327489</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01085963193327188</v>
+        <v>2.804862742777914e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.02056526020169258</v>
+        <v>0.001945095136761665</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01828906685113907</v>
+        <v>0.002498972695320845</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.03220487385988235</v>
+        <v>0.003006197046488523</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.004293466452509165</v>
+        <v>0.0008526695892214775</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.005762208253145218</v>
+        <v>0.008477748371660709</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006512303836643696</v>
+        <v>0.0004782708128914237</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01313016004860401</v>
+        <v>0.003883225843310356</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01073538884520531</v>
+        <v>0.001419221516698599</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.002954226452857256</v>
+        <v>0.0004517153138294816</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.005279817618429661</v>
+        <v>0.0006993231363594532</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.04010522738099098</v>
+        <v>0.005636791698634624</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.05685229599475861</v>
+        <v>0.003530039917677641</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.03276374936103821</v>
+        <v>0.00313562760129571</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.05088399723172188</v>
+        <v>0.01555540412664413</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01592567004263401</v>
+        <v>0.0009865406900644302</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.05370001494884491</v>
+        <v>0.003524516709148884</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.01181479636579752</v>
+        <v>0.01177293807268143</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.008689107373356819</v>
+        <v>0.005998227745294571</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.003026096615940332</v>
+        <v>0.0009577092132531106</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02003634534776211</v>
+        <v>0.002400750294327736</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.02379037998616695</v>
+        <v>0.002223522169515491</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.005501649808138609</v>
+        <v>0.00061582843773067</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01698100194334984</v>
+        <v>0.009557705372571945</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.007521156221628189</v>
+        <v>0.0009499677689746022</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.01831812225282192</v>
+        <v>0.003539712633937597</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.005713724065572023</v>
+        <v>0.00100650149397552</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.004666858352720737</v>
+        <v>1.403247006237507e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.003539554076269269</v>
+        <v>0.001642496907152236</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.003287930972874165</v>
+        <v>0.005247021559625864</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01216735318303108</v>
+        <v>0.006640097126364708</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.002356939949095249</v>
+        <v>0.004221108742058277</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.009165417402982712</v>
+        <v>0.01513036154210567</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.008013855665922165</v>
+        <v>0.002163348253816366</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.01309492625296116</v>
+        <v>0.004412437789142132</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.005585821345448494</v>
+        <v>0.005799256730824709</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001089228317141533</v>
+        <v>0.01145688816905022</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.005062876269221306</v>
+        <v>0.0008556304383091629</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.04493643343448639</v>
+        <v>0.001629136735573411</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0201444961130619</v>
+        <v>0.0003055972920265049</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01821928657591343</v>
+        <v>0.004651524126529694</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.00120135210454464</v>
+        <v>0.007486667484045029</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001587365753948689</v>
+        <v>0.0008153878152370453</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01508685573935509</v>
+        <v>0.003738550702109933</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.008359713479876518</v>
+        <v>0.004238019697368145</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.007604228332638741</v>
+        <v>0.004244640469551086</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.003419318934902549</v>
+        <v>0.00909077562391758</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01943687349557877</v>
+        <v>0.0009578454773873091</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02192867361009121</v>
+        <v>0.002063404303044081</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.04281352087855339</v>
+        <v>0.003833369351923466</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.02043170481920242</v>
+        <v>0.001689801923930645</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.03489942848682404</v>
+        <v>0.0008630002266727388</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.007145260460674763</v>
+        <v>0.003179987426847219</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.002295279409736395</v>
+        <v>0.0002568882773630321</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.009364751167595387</v>
+        <v>0.007930423133075237</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.02353363297879696</v>
+        <v>0.0004271510697435588</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02629201114177704</v>
+        <v>0.005946553312242031</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01722072437405586</v>
+        <v>0.001993354642763734</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01542518939822912</v>
+        <v>0.00119748676661402</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01308109052479267</v>
+        <v>0.006422300823032856</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.006004796829074621</v>
+        <v>0.001606349716894329</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001289004692807794</v>
+        <v>0.005007063504308462</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.008431935682892799</v>
+        <v>0.0006048413924872875</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0006442987360060215</v>
+        <v>0.0006353716598823667</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.01244431547820568</v>
+        <v>0.0003426781622692943</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01941974647343159</v>
+        <v>0.002493205945938826</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0335121676325798</v>
+        <v>0.004878704436123371</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.02077095024287701</v>
+        <v>0.004762632772326469</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02991493605077267</v>
+        <v>0.007197860162705183</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02252344042062759</v>
+        <v>0.0009175412706099451</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.05452702566981316</v>
+        <v>0.004548981785774231</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.007377774454653263</v>
+        <v>0.003720259759575129</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0208749808371067</v>
+        <v>0.0002383301907684654</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.01253201346844435</v>
+        <v>0.005175709258764982</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01553874649107456</v>
+        <v>0.002774021588265896</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.02382362261414528</v>
+        <v>0.002344351960346103</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.00218039914034307</v>
+        <v>0.0007008136599324644</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.008529524318873882</v>
+        <v>0.01172256842255592</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.003620522562414408</v>
+        <v>0.0008201742894016206</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02025839686393738</v>
+        <v>0.003288701875135303</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.005565166473388672</v>
+        <v>6.863940507173538e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.007800912484526634</v>
+        <v>6.197544280439615e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.00794245395809412</v>
+        <v>0.001134431455284357</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01934076473116875</v>
+        <v>0.004674355965107679</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.001301572076044977</v>
+        <v>0.0007295656832866371</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.008023245260119438</v>
+        <v>0.003599830204620957</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.006324599031358957</v>
+        <v>0.006530233658850193</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01055467408150434</v>
+        <v>0.002436778275296092</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01233977917581797</v>
+        <v>9.861968283075839e-05</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.006559205241501331</v>
+        <v>0.001734153600409627</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.004411999601870775</v>
+        <v>0.001311797183007002</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.01003940869122744</v>
+        <v>0.002892911899834871</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01200099475681782</v>
+        <v>0.009675424546003342</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.09283165633678436</v>
+        <v>0.004087901208549738</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04386388137936592</v>
+        <v>0.0004091411828994751</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.04694147780537605</v>
+        <v>0.00502668647095561</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.08355224132537842</v>
+        <v>0.003473040880635381</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.007009169552475214</v>
+        <v>0.01106570567935705</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.004707308486104012</v>
+        <v>0.008440817706286907</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.006182551383972168</v>
+        <v>0.002402956364676356</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0009846037719398737</v>
+        <v>0.01278206892311573</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.02772267907857895</v>
+        <v>0.002424918347969651</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.04324251040816307</v>
+        <v>0.0006890299264341593</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.009559833444654942</v>
+        <v>0.006131410598754883</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.007417595013976097</v>
+        <v>0.008901599794626236</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.07330981642007828</v>
+        <v>0.00126697332598269</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.005438587628304958</v>
+        <v>0.001758837141096592</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.01005552150309086</v>
+        <v>0.004840226378291845</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.00611924147233367</v>
+        <v>2.968165790662169e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.01975055783987045</v>
+        <v>0.006239187903702259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0005372291198000312</v>
+        <v>6.739278614986688e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>0.009378169663250446</v>
+        <v>0.000469164369860664</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004458883195184171</v>
+        <v>0.0001605214783921838</v>
       </c>
       <c r="D11" t="n">
-        <v>0.005920079536736012</v>
+        <v>0.0002454447676427662</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008743374608457088</v>
+        <v>8.858002547640353e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004665074869990349</v>
+        <v>0.0004198789538349956</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002216716296970844</v>
+        <v>0.0002676182193681598</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002942520950455219</v>
+        <v>0.000434136250987649</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002215155167505145</v>
+        <v>4.148352309130132e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004252875805832446</v>
+        <v>0.0001300890580751002</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006905394606292248</v>
+        <v>0.0006415144307538867</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0008162524318322539</v>
+        <v>6.856804247945547e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006052845157682896</v>
+        <v>6.746417057001963e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009504662826657295</v>
+        <v>0.0004541910602711141</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006298146676272154</v>
+        <v>0.0005184580222703516</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002487380290403962</v>
+        <v>7.962682138895616e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001110595883801579</v>
+        <v>0.0002001474349526688</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001660001231357455</v>
+        <v>0.0002200781309511513</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0008985632448457181</v>
+        <v>0.0001415227889083326</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002475137589499354</v>
+        <v>8.645255002193153e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>0.000275459373369813</v>
+        <v>0.0001640806294744834</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0003587850660551339</v>
+        <v>4.898184852208942e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0004832989070564508</v>
+        <v>7.305172039195895e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002832954749464989</v>
+        <v>6.141816265881062e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001467116526328027</v>
+        <v>9.638814663048834e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0004336054553277791</v>
+        <v>0.0002391437737969682</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.413702016696334e-05</v>
+        <v>4.162780896876939e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0005020112730562687</v>
+        <v>0.0002241905458504334</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001716303871944547</v>
+        <v>1.185929795610718e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009163090726360679</v>
+        <v>4.553537291940302e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.003892027074471116</v>
+        <v>1.251253706868738e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.003368167905136943</v>
+        <v>0.0001750112714944407</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001587157021276653</v>
+        <v>0.0001800991158233956</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.001326402998529375</v>
+        <v>0.0001819791650632396</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0004513754392974079</v>
+        <v>0.0003175849851686507</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.000426470476668328</v>
+        <v>0.0001185612345580012</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0009435907704755664</v>
+        <v>9.325984865427017e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001706238719634712</v>
+        <v>0.0001227968605235219</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.535417868581135e-05</v>
+        <v>0.0001090367659344338</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0001849181135185063</v>
+        <v>7.88901379564777e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001470978138968349</v>
+        <v>0.0001351095706922933</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0001693968661129475</v>
+        <v>4.791236278833821e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.001370264333672822</v>
+        <v>2.76844366453588e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0001052386360242963</v>
+        <v>0.0001292885863222182</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.001169383060187101</v>
+        <v>1.282897210330702e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.002583720255643129</v>
+        <v>0.0001021618227241561</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.00808323360979557</v>
+        <v>0.0005694960709661245</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0002731748390942812</v>
+        <v>7.388625090243295e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001186377368867397</v>
+        <v>3.867492705467157e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.002057783305644989</v>
+        <v>0.0002681404585018754</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003892394248396158</v>
+        <v>0.0003164065419696271</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.002573630772531033</v>
+        <v>8.846705168252811e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0003768247552216053</v>
+        <v>7.54180146032013e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.206947490572929e-05</v>
+        <v>7.987247226992622e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0001630258047953248</v>
+        <v>0.0002168197388527915</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.001231601927429438</v>
+        <v>4.777049252879806e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0019299800042063</v>
+        <v>1.666697789914906e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0009049731306731701</v>
+        <v>0.0002616027777548879</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.008036083541810513</v>
+        <v>0.000116147450171411</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001800565049052238</v>
+        <v>6.517869769595563e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001498891040682793</v>
+        <v>0.0001012079228530638</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001314660534262657</v>
+        <v>0.000432751519838348</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.002448203042149544</v>
+        <v>0.0001124292175518349</v>
       </c>
       <c r="BL11" t="n">
-        <v>5.472631892189384e-05</v>
+        <v>5.653937478200532e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.002799496985971928</v>
+        <v>0.0001797704171622172</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.001223565544933081</v>
+        <v>6.368124741129577e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.001421748893335462</v>
+        <v>0.0001263760204892606</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.000477480876725167</v>
+        <v>0.0001303521858062595</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001226326683536172</v>
+        <v>0.000232421065447852</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.00232549337670207</v>
+        <v>8.383522799704224e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.000291425792966038</v>
+        <v>3.787528839893639e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0005523611325770617</v>
+        <v>0.0001695849059615284</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.00128963787574321</v>
+        <v>9.384901204612106e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.003582186764106154</v>
+        <v>0.0003581119526643306</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.001627269084565341</v>
+        <v>6.051083255442791e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.002112893387675285</v>
+        <v>0.000341206876328215</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.00154685543384403</v>
+        <v>9.658683848101646e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0002675786672625691</v>
+        <v>0.0001073574967449531</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0004338654107414186</v>
+        <v>2.433934059808962e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0002858277584891766</v>
+        <v>0.0001005408412311226</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.000158665410708636</v>
+        <v>5.736117600463331e-05</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0004282762238290161</v>
+        <v>0.0001728144125081599</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001953479833900928</v>
+        <v>0.0001509433495812118</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0009060734300874174</v>
+        <v>8.584975148551166e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.001192742027342319</v>
+        <v>2.856434366549365e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0005309697589837015</v>
+        <v>7.534530595876276e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0008210553205572069</v>
+        <v>0.0001257175608770922</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001137165818363428</v>
+        <v>5.780532956123352e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0003405089664738625</v>
+        <v>1.086496649804758e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.000104092905530706</v>
+        <v>5.893916750210337e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.002798569388687611</v>
+        <v>0.0001379025634378195</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.001226628664880991</v>
+        <v>0.0003319536044728011</v>
       </c>
       <c r="CO11" t="n">
-        <v>4.309867654228583e-05</v>
+        <v>0.0001422937930328771</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.001289253472350538</v>
+        <v>0.0001540313824079931</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0007353773107752204</v>
+        <v>9.748798765940592e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0005887844599783421</v>
+        <v>6.511867832159624e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0003215722390450537</v>
+        <v>0.0001950454752659425</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001594147644937038</v>
+        <v>1.500453709013527e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0008334286976605654</v>
+        <v>4.501177681959234e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0003962882037740201</v>
+        <v>0.0001553734764456749</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.001370395999401808</v>
+        <v>0.0001113903199438937</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001082648173905909</v>
+        <v>5.960481212241575e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001731563243083656</v>
+        <v>4.448382242117077e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0007122065289877355</v>
+        <v>6.669557478744537e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0006509086233563721</v>
+        <v>0.0001290028885705397</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.001137288636527956</v>
+        <v>1.046015495376196e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0002256844600196928</v>
+        <v>1.551838977320585e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>7.819884922355413e-05</v>
+        <v>1.149510353570804e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.271146513521671e-06</v>
+        <v>9.559527097735554e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003096144879236817</v>
+        <v>0.0001823307247832417</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.000249486678512767</v>
+        <v>9.200481872539967e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.003758771810680628</v>
+        <v>8.408824214711785e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.001733872108161449</v>
+        <v>0.0001472909934818745</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0003080602618865669</v>
+        <v>4.765913035953417e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.002449400490149856</v>
+        <v>3.220623329980299e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001154822297394276</v>
+        <v>0.0002627815993037075</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.359203062951565e-05</v>
+        <v>0.0002021988912019879</v>
       </c>
       <c r="DN11" t="n">
-        <v>8.833225001581013e-05</v>
+        <v>7.781415479257703e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0005960797425359488</v>
+        <v>6.251955346670002e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001771008362993598</v>
+        <v>2.385931293247268e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001151284785009921</v>
+        <v>0.0001273101515835151</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0001354897685814649</v>
+        <v>0.000117892304842826</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0006092680850997567</v>
+        <v>3.827784166787751e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0001603098644409329</v>
+        <v>3.693530743476003e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001793521078070626</v>
+        <v>0.0001707159099169075</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0001249229826498777</v>
+        <v>1.48625558722415e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.000523378315847367</v>
+        <v>6.823068542871624e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.001066152821294963</v>
+        <v>2.506381861167029e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0008841590024530888</v>
+        <v>1.399537723045796e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0004146377323195338</v>
+        <v>2.875732934626285e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>8.452520705759525e-05</v>
+        <v>2.755303285084665e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0005118890549056232</v>
+        <v>0.0001563708938192576</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0002360439975745976</v>
+        <v>2.468318416504189e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007404807838611305</v>
+        <v>0.0001039974595187232</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0009055790142156184</v>
+        <v>0.0002435250498820096</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0009839673293754458</v>
+        <v>0.0001164753048215061</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0001853236462920904</v>
+        <v>4.109674773644656e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0002831912133842707</v>
+        <v>0.0001249017659574747</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.00103259552270174</v>
+        <v>3.927131547243334e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.00156449805945158</v>
+        <v>0.0001158119121100754</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0001664188894210383</v>
+        <v>0.0001012451612041332</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.001576965674757957</v>
+        <v>3.777474194066599e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0006390259368345141</v>
+        <v>5.118910485180095e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001973181642824784</v>
+        <v>5.6690438213991e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001244559767656028</v>
+        <v>0.0001640365371713415</v>
       </c>
       <c r="EP11" t="n">
-        <v>3.807892062468454e-05</v>
+        <v>0.0001110626544686966</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.00121990661136806</v>
+        <v>8.098386751953512e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001621320727281272</v>
+        <v>3.188186383340508e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>8.029106538742781e-06</v>
+        <v>0.000201236514840275</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001713814563117921</v>
+        <v>0.0001238618278875947</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.00200862274505198</v>
+        <v>4.90486272610724e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0007498586783185601</v>
+        <v>8.445653656963259e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0006301311077550054</v>
+        <v>5.381654773373157e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0005736853927373886</v>
+        <v>0.0001798531011445448</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001262053614482284</v>
+        <v>0.0001559826341690496</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0006705005653202534</v>
+        <v>5.975141539238393e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.001422646455466747</v>
+        <v>7.727699994575232e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0005065292934887111</v>
+        <v>3.945281059714034e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.001329211983829737</v>
+        <v>9.847438195720315e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001438570790924132</v>
+        <v>6.253755418583751e-05</v>
       </c>
       <c r="FE11" t="n">
-        <v>8.576997788622975e-05</v>
+        <v>1.648993929848075e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0005308157997205853</v>
+        <v>5.913359927944839e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.001042570336721838</v>
+        <v>5.746363603975624e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0008262265473604202</v>
+        <v>0.0001427005627192557</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.001258705044165254</v>
+        <v>2.70978853222914e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.001293038250878453</v>
+        <v>0.0001796437136363238</v>
       </c>
       <c r="FK11" t="n">
-        <v>1.999113374040462e-05</v>
+        <v>0.0001042500152834691</v>
       </c>
       <c r="FL11" t="n">
-        <v>4.097429336979985e-05</v>
+        <v>0.000100579287391156</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.000398348638555035</v>
+        <v>9.26939828786999e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0007938744965940714</v>
+        <v>0.0002458032395225018</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.001319132279604673</v>
+        <v>9.901197336148471e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.001899370225146413</v>
+        <v>0.0001207894383696839</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001220829668454826</v>
+        <v>0.0001006826933007687</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0001671269274083897</v>
+        <v>0.0001102509995689616</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.00291860569268465</v>
+        <v>3.921931056538597e-05</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0007616856601089239</v>
+        <v>0.0002272517594974488</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.00147081445902586</v>
+        <v>0.0001527869026176631</v>
       </c>
       <c r="FV11" t="n">
-        <v>5.44659560546279e-05</v>
+        <v>8.75873229233548e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>5.344286910258234e-05</v>
+        <v>0.0003001309814862907</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0002655450953170657</v>
+        <v>0.0001211308917845599</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001900271279737353</v>
+        <v>0.0002382722304901108</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.001259549986571074</v>
+        <v>0.0001109618606278673</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001726717018755153</v>
+        <v>0.0001348704099655151</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.001068589510396123</v>
+        <v>3.456672857282683e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.001263096695765853</v>
+        <v>0.000196208551642485</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0001206852030009031</v>
+        <v>0.0001863812940428033</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001315810601226985</v>
+        <v>7.932955486467108e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0007039072224870324</v>
+        <v>8.74979596119374e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001498022116720676</v>
+        <v>0.0002117803524015471</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0001331705279881135</v>
+        <v>9.140893234871328e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001309155020862818</v>
+        <v>0.0009384371805936098</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001268876803806052</v>
+        <v>0.0001590921165188774</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0009172582649625838</v>
+        <v>0.000852359808050096</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004311410593800247</v>
+        <v>3.339670365676284e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0002406470448477194</v>
+        <v>0.0005108205368742347</v>
       </c>
       <c r="G12" t="n">
-        <v>8.815903856884688e-05</v>
+        <v>0.0003717329527717084</v>
       </c>
       <c r="H12" t="n">
-        <v>9.006276377476752e-05</v>
+        <v>0.0003531495458446443</v>
       </c>
       <c r="I12" t="n">
-        <v>7.581739919260144e-05</v>
+        <v>1.396552761434577e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002248894888907671</v>
+        <v>2.175105328205973e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0008965419256128371</v>
+        <v>0.0008415166521444917</v>
       </c>
       <c r="L12" t="n">
-        <v>1.582644836162217e-05</v>
+        <v>0.000248680473305285</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0009299691300839186</v>
+        <v>0.001150385476648808</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0006225486285984516</v>
+        <v>0.0004471438587643206</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004432248824741691</v>
+        <v>0.0005646346835419536</v>
       </c>
       <c r="P12" t="n">
-        <v>1.878997136373073e-05</v>
+        <v>0.0003153203579131514</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001134970807470381</v>
+        <v>4.996487405151129e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001544146507512778</v>
+        <v>0.0001695778919383883</v>
       </c>
       <c r="S12" t="n">
-        <v>4.357539728516713e-05</v>
+        <v>6.623296940233558e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0002459254756104201</v>
+        <v>2.158247662009671e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>6.626059985137545e-07</v>
+        <v>9.867823246167973e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>6.232029409147799e-05</v>
+        <v>5.596754999714904e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001007237005978823</v>
+        <v>0.000181792929652147</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0001979981025215238</v>
+        <v>0.0002456945076119155</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0001811674301279709</v>
+        <v>0.000162586075020954</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001108503784053028</v>
+        <v>0.0001561177341500297</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.759521496249363e-05</v>
+        <v>3.991962876170874e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0001469352282583714</v>
+        <v>0.0001434947334928438</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0002870710450224578</v>
+        <v>2.608445356599987e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.897536564385518e-05</v>
+        <v>0.0001187573725474067</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001263035810552537</v>
+        <v>0.0001831184781622142</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0001977303036255762</v>
+        <v>0.0001678240223554894</v>
       </c>
       <c r="AG12" t="n">
-        <v>8.061715197982267e-05</v>
+        <v>0.0004316671402193606</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0001391584955854341</v>
+        <v>0.0001349962258245796</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.89523115195334e-05</v>
+        <v>0.0001816288713598624</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.878007636463735e-06</v>
+        <v>0.0001893981680041179</v>
       </c>
       <c r="AK12" t="n">
-        <v>7.307079067686573e-05</v>
+        <v>4.314308171160519e-06</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.000126984145026654</v>
+        <v>0.0002845585695467889</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.169108094880357e-05</v>
+        <v>0.0001425860828021541</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.907622522092424e-05</v>
+        <v>0.0002313050208613276</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001787161018000916</v>
+        <v>8.993203664431348e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.397000783588737e-05</v>
+        <v>0.0002369751309743151</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.959938163054176e-05</v>
+        <v>0.0001040755887515843</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.918892252841033e-05</v>
+        <v>5.428263102658093e-05</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.219792754156515e-05</v>
+        <v>6.956574361538514e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0001438245526514947</v>
+        <v>4.578378138830885e-05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0009740805253386497</v>
+        <v>0.0004702563746832311</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.43249132836354e-06</v>
+        <v>0.0002879704989027232</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.273308827076107e-05</v>
+        <v>0.0002249104145448655</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.604023029562086e-05</v>
+        <v>0.0007359005394391716</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.88283512822818e-06</v>
+        <v>0.0004522321396507323</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.646711310371757e-05</v>
+        <v>6.173119618324563e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.048619014909491e-05</v>
+        <v>9.5216921181418e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.085452044615522e-05</v>
+        <v>9.253470489056781e-05</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.004800651571713e-05</v>
+        <v>0.0001026602330966853</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0001891506253741682</v>
+        <v>0.0002047700982075185</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002440452371956781</v>
+        <v>0.0001413859135936946</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0002735243469942361</v>
+        <v>7.492798613384366e-05</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0005883642588742077</v>
+        <v>0.000380953773856163</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0001415311417076737</v>
+        <v>0.0001087031268980354</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0002475779911037534</v>
+        <v>0.0002185825724154711</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.736123709240928e-05</v>
+        <v>0.0002595892583485693</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0001383643102599308</v>
+        <v>0.000154260327690281</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0001775436830939725</v>
+        <v>5.940600749454461e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001872254651971161</v>
+        <v>2.876560029108077e-05</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001087020864360966</v>
+        <v>2.451008185744286e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>2.945619053207338e-05</v>
+        <v>0.0001681295107118785</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0001479211496189237</v>
+        <v>9.922909521264955e-05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.572853403165936e-05</v>
+        <v>9.361820048070513e-07</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0002610807423479855</v>
+        <v>1.822928243200295e-05</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0001725725596770644</v>
+        <v>5.509879702003673e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.27794509252999e-06</v>
+        <v>6.283697439357638e-05</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.204879122786224e-05</v>
+        <v>3.060800008825026e-05</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0004710731736849993</v>
+        <v>0.0003998738247901201</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001436459278920665</v>
+        <v>0.0001438486797269434</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0001339618611382321</v>
+        <v>0.0003567198873497546</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.168983999377815e-05</v>
+        <v>0.0001231980131706223</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001537362113595009</v>
+        <v>0.0003552617854438722</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.18556126835756e-05</v>
+        <v>0.0001324190088780597</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.556123970658518e-05</v>
+        <v>3.598147304728627e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.865456553990953e-05</v>
+        <v>8.951442578108981e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.929780698148534e-05</v>
+        <v>3.245915286242962e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0002398816141067073</v>
+        <v>0.0002771716681309044</v>
       </c>
       <c r="CF12" t="n">
-        <v>7.001832273090258e-05</v>
+        <v>5.840069206897169e-06</v>
       </c>
       <c r="CG12" t="n">
-        <v>4.639116741600446e-05</v>
+        <v>0.0003136633895337582</v>
       </c>
       <c r="CH12" t="n">
-        <v>4.461724165594205e-05</v>
+        <v>1.234329556609737e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>6.933067925274372e-05</v>
+        <v>8.912262273952365e-05</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0001009207917377353</v>
+        <v>5.211740790400654e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.394323771819472e-05</v>
+        <v>8.568575140088797e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.672692789928988e-05</v>
+        <v>2.21867230720818e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0002495863300282508</v>
+        <v>0.0001892571890493855</v>
       </c>
       <c r="CN12" t="n">
-        <v>8.741091005504131e-05</v>
+        <v>0.0001815153082134202</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.33943748450838e-05</v>
+        <v>0.0003653549938462675</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0003315983340144157</v>
+        <v>0.0004461448406800628</v>
       </c>
       <c r="CQ12" t="n">
-        <v>9.023935126606375e-05</v>
+        <v>4.199765680823475e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0001685701718088239</v>
+        <v>0.0001987474679481238</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0001186503723147325</v>
+        <v>0.0001536052586743608</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001853329013101757</v>
+        <v>3.045136691071093e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>2.684629725990817e-05</v>
+        <v>7.781288877595216e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>4.708896085503511e-05</v>
+        <v>7.048869974823901e-06</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0001814593124436215</v>
+        <v>0.0002452188055031002</v>
       </c>
       <c r="CX12" t="n">
-        <v>9.424507879884914e-05</v>
+        <v>4.394134157337248e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>9.93884532363154e-05</v>
+        <v>0.0003249541041441262</v>
       </c>
       <c r="CZ12" t="n">
-        <v>3.505940549075603e-05</v>
+        <v>0.0001037606125464663</v>
       </c>
       <c r="DA12" t="n">
-        <v>6.081300307414494e-05</v>
+        <v>9.28106383071281e-05</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0001056606852216646</v>
+        <v>3.846361505566165e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.540668356232345e-05</v>
+        <v>9.002922888612375e-05</v>
       </c>
       <c r="DD12" t="n">
-        <v>9.964714990928769e-06</v>
+        <v>2.614002187328879e-05</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001310277584707364</v>
+        <v>0.0001527552667539567</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0001674273662501946</v>
+        <v>0.0002391813322901726</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.266907565877773e-05</v>
+        <v>8.983333827927709e-07</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0003254255279898643</v>
+        <v>0.0003207586123608053</v>
       </c>
       <c r="DI12" t="n">
-        <v>6.230618600966409e-05</v>
+        <v>0.0001759488368406892</v>
       </c>
       <c r="DJ12" t="n">
-        <v>5.730968769057654e-05</v>
+        <v>0.0003787256428040564</v>
       </c>
       <c r="DK12" t="n">
-        <v>9.910375956678763e-05</v>
+        <v>2.08351466426393e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>7.027578249108046e-06</v>
+        <v>0.0005289921537041664</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.80857241502963e-05</v>
+        <v>0.0002488052705302835</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001006901147775352</v>
+        <v>1.399456232320517e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>5.456960934679955e-05</v>
+        <v>0.0001775062555680051</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001507487904746085</v>
+        <v>9.901159501168877e-06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001325097837252542</v>
+        <v>0.0002036086516454816</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0001988692383747548</v>
+        <v>5.366211553337052e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>5.9983525716234e-05</v>
+        <v>0.0001518955687060952</v>
       </c>
       <c r="DT12" t="n">
-        <v>3.9301099604927e-05</v>
+        <v>0.000170000217622146</v>
       </c>
       <c r="DU12" t="n">
-        <v>6.732516339980066e-07</v>
+        <v>6.372550706146285e-05</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.040711792185903e-05</v>
+        <v>0.0002944123698398471</v>
       </c>
       <c r="DW12" t="n">
-        <v>7.168322554207407e-06</v>
+        <v>4.111352973268367e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>7.854327122913674e-05</v>
+        <v>3.880884469253942e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0001134834965341724</v>
+        <v>0.0002745213569141924</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0001690649223746732</v>
+        <v>0.0001178223901661113</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0001504169631516561</v>
+        <v>8.921218977775425e-05</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.706401963019744e-05</v>
+        <v>6.677889905404299e-05</v>
       </c>
       <c r="EC12" t="n">
-        <v>8.409369911532849e-05</v>
+        <v>3.476058191154152e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>6.352931086439639e-05</v>
+        <v>0.0003959400055464357</v>
       </c>
       <c r="EE12" t="n">
-        <v>5.364214302971959e-05</v>
+        <v>0.0004177544906269759</v>
       </c>
       <c r="EF12" t="n">
-        <v>1.106700801756233e-05</v>
+        <v>5.275903095025569e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.000125414808280766</v>
+        <v>0.0001356194115942344</v>
       </c>
       <c r="EH12" t="n">
-        <v>1.491057628300041e-05</v>
+        <v>0.0001639833790250123</v>
       </c>
       <c r="EI12" t="n">
-        <v>6.594032311113551e-05</v>
+        <v>0.0002787689445540309</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.000176887697307393</v>
+        <v>0.0001224332663696259</v>
       </c>
       <c r="EK12" t="n">
-        <v>3.66684325854294e-05</v>
+        <v>7.082446973072365e-05</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0001988561998587102</v>
+        <v>4.285652539692819e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>9.039492579177022e-05</v>
+        <v>8.594399332650937e-06</v>
       </c>
       <c r="EN12" t="n">
-        <v>4.557834472507238e-06</v>
+        <v>6.670394213870168e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>9.209415293298662e-05</v>
+        <v>6.728724110871553e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0001548899308545515</v>
+        <v>0.0002561694127507508</v>
       </c>
       <c r="EQ12" t="n">
-        <v>5.160000728210434e-05</v>
+        <v>6.683931133011356e-06</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001124555710703135</v>
+        <v>0.0002653092087712139</v>
       </c>
       <c r="ES12" t="n">
-        <v>1.229869667440653e-05</v>
+        <v>7.361787720583379e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0002798116765916348</v>
+        <v>2.755446257651784e-05</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001905796234495938</v>
+        <v>0.0001126556162489578</v>
       </c>
       <c r="EV12" t="n">
-        <v>3.180438943672925e-05</v>
+        <v>9.851876529864967e-05</v>
       </c>
       <c r="EW12" t="n">
-        <v>4.967980203218758e-06</v>
+        <v>0.0001735574187478051</v>
       </c>
       <c r="EX12" t="n">
-        <v>2.73429395747371e-06</v>
+        <v>3.440585714997724e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0001893652806757018</v>
+        <v>0.0002891170443035662</v>
       </c>
       <c r="EZ12" t="n">
-        <v>4.197650196147151e-05</v>
+        <v>1.712658922770061e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001010125706670806</v>
+        <v>0.0003589533444028348</v>
       </c>
       <c r="FB12" t="n">
-        <v>3.837325834865624e-07</v>
+        <v>1.750160299707204e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0001032480940921232</v>
+        <v>0.0001139505911851302</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.000115158487460576</v>
+        <v>6.9361394707812e-06</v>
       </c>
       <c r="FE12" t="n">
-        <v>7.91608908912167e-06</v>
+        <v>8.722441998543218e-05</v>
       </c>
       <c r="FF12" t="n">
-        <v>2.97171591228107e-05</v>
+        <v>1.274460828426527e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>2.209882950410247e-06</v>
+        <v>8.121718565234914e-05</v>
       </c>
       <c r="FH12" t="n">
-        <v>3.991441553807817e-05</v>
+        <v>9.545446664560586e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>6.638422928517684e-05</v>
+        <v>0.0001114466140279546</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0002181882155127823</v>
+        <v>8.711643749848008e-05</v>
       </c>
       <c r="FK12" t="n">
-        <v>9.113239502767101e-05</v>
+        <v>8.68507195264101e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>2.339834463782609e-05</v>
+        <v>3.137974272249267e-05</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.000119228134281002</v>
+        <v>3.800703416345641e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>3.423721136641689e-05</v>
+        <v>4.884257214143872e-05</v>
       </c>
       <c r="FO12" t="n">
-        <v>9.055656846612692e-05</v>
+        <v>0.000212018407182768</v>
       </c>
       <c r="FP12" t="n">
-        <v>7.528275455115363e-05</v>
+        <v>0.0001624089491087943</v>
       </c>
       <c r="FQ12" t="n">
-        <v>5.156892439117655e-05</v>
+        <v>0.0001991687895497307</v>
       </c>
       <c r="FR12" t="n">
-        <v>1.432594217476435e-05</v>
+        <v>0.0002458339149598032</v>
       </c>
       <c r="FS12" t="n">
-        <v>8.94199256435968e-05</v>
+        <v>0.0001340628659818321</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0002018777740886435</v>
+        <v>0.0005977441905997694</v>
       </c>
       <c r="FU12" t="n">
-        <v>8.128501212922856e-05</v>
+        <v>0.0001074094689101912</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.000198200621525757</v>
+        <v>7.667638419661671e-05</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0001367505610687658</v>
+        <v>0.0003498901787679642</v>
       </c>
       <c r="FX12" t="n">
-        <v>9.613155270926654e-05</v>
+        <v>2.761007635854185e-05</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0001944297400768846</v>
+        <v>0.0001481142389820889</v>
       </c>
       <c r="FZ12" t="n">
-        <v>4.859735781792551e-05</v>
+        <v>4.923763481201604e-05</v>
       </c>
       <c r="GA12" t="n">
-        <v>2.089311783493031e-05</v>
+        <v>0.0002515147789381444</v>
       </c>
       <c r="GB12" t="n">
-        <v>2.042797677859198e-05</v>
+        <v>0.0003054638509638608</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0002173972607124597</v>
+        <v>9.730010060593486e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001018244656734169</v>
+        <v>0.0002369137364439666</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0002532336511649191</v>
+        <v>0.0002877080987673253</v>
       </c>
       <c r="GF12" t="n">
-        <v>8.08239565230906e-05</v>
+        <v>5.371683073462918e-06</v>
       </c>
       <c r="GG12" t="n">
-        <v>2.381339254498016e-05</v>
+        <v>1.374586827296298e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00952279195189476</v>
+        <v>0.01132869906723499</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1173035055398941</v>
+        <v>0.06993485987186432</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01845115050673485</v>
+        <v>0.006484139710664749</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05063094571232796</v>
+        <v>0.01694601774215698</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04209469258785248</v>
+        <v>0.01148147508502007</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07873766124248505</v>
+        <v>0.03819938004016876</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003016657195985317</v>
+        <v>0.04301241040229797</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01889844611287117</v>
+        <v>0.04282189905643463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.006217098329216242</v>
+        <v>0.0009199748747050762</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02089240029454231</v>
+        <v>0.02096657082438469</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1025754287838936</v>
+        <v>0.09767512232065201</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003453886369243264</v>
+        <v>0.01666194945573807</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06099475175142288</v>
+        <v>0.05633736401796341</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0371982529759407</v>
+        <v>0.02597564086318016</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08661787956953049</v>
+        <v>0.09379332512617111</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01314426399767399</v>
+        <v>0.04659772291779518</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01912647113204002</v>
+        <v>0.01244914531707764</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008660534396767616</v>
+        <v>0.008201331831514835</v>
       </c>
       <c r="S13" t="n">
-        <v>0.004471738822758198</v>
+        <v>0.003447031136602163</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01671222411096096</v>
+        <v>0.003367329016327858</v>
       </c>
       <c r="U13" t="n">
-        <v>0.002367703709751368</v>
+        <v>0.03080863505601883</v>
       </c>
       <c r="V13" t="n">
-        <v>0.007801709696650505</v>
+        <v>0.0368662141263485</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003218080382794142</v>
+        <v>0.05947123840451241</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01007227413356304</v>
+        <v>0.02953949384391308</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01377659384161234</v>
+        <v>0.0003728698939085007</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001668404787778854</v>
+        <v>0.01026939228177071</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.009693356230854988</v>
+        <v>0.01430772989988327</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005092751700431108</v>
+        <v>0.04899435117840767</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.003467065282166004</v>
+        <v>0.01981558464467525</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01007261499762535</v>
+        <v>0.001431338838301599</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01716174185276031</v>
+        <v>0.04448260366916656</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.003007993102073669</v>
+        <v>0.0220248494297266</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.007533814758062363</v>
+        <v>0.02968736365437508</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01178762037307024</v>
+        <v>0.02570305950939655</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0007054097950458527</v>
+        <v>0.03318202495574951</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.006762797012925148</v>
+        <v>0.02046832069754601</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01872967928647995</v>
+        <v>0.01852536574006081</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01176429353654385</v>
+        <v>0.01515520177781582</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0007229710463434458</v>
+        <v>0.003400143003091216</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.393320366740227e-05</v>
+        <v>0.02269360795617104</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002368950750678778</v>
+        <v>0.02976410835981369</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01837439276278019</v>
+        <v>0.03221188485622406</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003915336448699236</v>
+        <v>0.02007976919412613</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01397239603102207</v>
+        <v>0.02242312021553516</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.006415027193725109</v>
+        <v>0.005499478429555893</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.01808792352676392</v>
+        <v>0.01480304263532162</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.09418904781341553</v>
+        <v>0.1574593633413315</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.002502634190022945</v>
+        <v>0.04543352499604225</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.003535816445946693</v>
+        <v>0.02838798612356186</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.004029207397252321</v>
+        <v>0.05330155789852142</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0236094556748867</v>
+        <v>0.08363717794418335</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.002411207184195518</v>
+        <v>0.06463652849197388</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0110502727329731</v>
+        <v>0.04200225695967674</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001657956978306174</v>
+        <v>0.02656486444175243</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.005668201483786106</v>
+        <v>0.04017520323395729</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04432246834039688</v>
+        <v>0.01034962013363838</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0407196506857872</v>
+        <v>0.04338696971535683</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004824317526072264</v>
+        <v>0.001887693651951849</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03049779124557972</v>
+        <v>0.0483773872256279</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.03576338663697243</v>
+        <v>0.01096869260072708</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.004472848027944565</v>
+        <v>0.006972247269004583</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.02758168429136276</v>
+        <v>0.03846044838428497</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01585804671049118</v>
+        <v>0.009214537218213081</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.006630958057940006</v>
+        <v>0.008085130713880062</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03504707664251328</v>
+        <v>0.03671551868319511</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01633560284972191</v>
+        <v>0.003434567712247372</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02316585555672646</v>
+        <v>0.001874952577054501</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03255705535411835</v>
+        <v>0.02248681709170341</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01314207818359137</v>
+        <v>0.006166960578411818</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0009181257337331772</v>
+        <v>0.02078261785209179</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006739247124642134</v>
+        <v>0.0004508348647505045</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.00760864932090044</v>
+        <v>0.005716520827263594</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01062916219234467</v>
+        <v>0.03641455993056297</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04281285032629967</v>
+        <v>0.06440848857164383</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0123054925352335</v>
+        <v>0.02167505770921707</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02049556002020836</v>
+        <v>0.07611552625894547</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0005980136338621378</v>
+        <v>0.07515964657068253</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.005285041872411966</v>
+        <v>0.07459376752376556</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007442552130669355</v>
+        <v>0.02327099442481995</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.01382571272552013</v>
+        <v>0.0003250930458307266</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.005783268250524998</v>
+        <v>0.01883961074054241</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0008796337060630322</v>
+        <v>0.01653021387755871</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01890171319246292</v>
+        <v>0.02190075628459454</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01215391512960196</v>
+        <v>0.004275758285075426</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01211087126284838</v>
+        <v>0.008295480161905289</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003605774603784084</v>
+        <v>0.01305492036044598</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01350799761712551</v>
+        <v>0.02479217760264874</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.004707156680524349</v>
+        <v>5.446988507173955e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.00315414578653872</v>
+        <v>0.006010466255247593</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.006048705894500017</v>
+        <v>0.003139654872938991</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02942556887865067</v>
+        <v>0.05392542853951454</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.03567132726311684</v>
+        <v>0.09039749950170517</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001306868274696171</v>
+        <v>0.007995178923010826</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.006726229097694159</v>
+        <v>0.0519946962594986</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.03123705089092255</v>
+        <v>0.04162611439824104</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.009364104829728603</v>
+        <v>0.0958796888589859</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.002157948445528746</v>
+        <v>0.01580430008471012</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.02332540228962898</v>
+        <v>0.01736752316355705</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01688654720783234</v>
+        <v>0.02498419582843781</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001261347904801369</v>
+        <v>0.02104068174958229</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.013482965528965</v>
+        <v>0.01792280003428459</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01114262267947197</v>
+        <v>0.007073785178363323</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01691212132573128</v>
+        <v>0.003457464510574937</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.00133485859259963</v>
+        <v>0.01024341303855181</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01415535807609558</v>
+        <v>0.01368463970720768</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.00504703726619482</v>
+        <v>0.006550340447574854</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.006615600548684597</v>
+        <v>0.0033511808142066</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.002193843945860863</v>
+        <v>0.00437546893954277</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.01406339649111032</v>
+        <v>0.009027887135744095</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02815834805369377</v>
+        <v>0.01299264840781689</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.009195119142532349</v>
+        <v>0.04293869063258171</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.04039281979203224</v>
+        <v>0.005295782350003719</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001029463717713952</v>
+        <v>0.02993007190525532</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01280537061393261</v>
+        <v>0.04816187918186188</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02618958055973053</v>
+        <v>0.03025106899440289</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.01383077539503574</v>
+        <v>0.004600482061505318</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.01433319691568613</v>
+        <v>0.03746847435832024</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.007688334677368402</v>
+        <v>0.02898680232465267</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01834256388247013</v>
+        <v>0.02795714884996414</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.007551479153335094</v>
+        <v>0.0005724290385842323</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.002086384687572718</v>
+        <v>0.06696957349777222</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.007567388471215963</v>
+        <v>0.03679313883185387</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.007674754597246647</v>
+        <v>0.02259069308638573</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.006025590933859348</v>
+        <v>0.01014280132949352</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.01062637381255627</v>
+        <v>0.02355408109724522</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.003704957431182265</v>
+        <v>0.008179126307368279</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.00126610416918993</v>
+        <v>0.01731768995523453</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001279412535950541</v>
+        <v>0.003985233139246702</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.00908871553838253</v>
+        <v>0.04432834684848785</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.009471580386161804</v>
+        <v>0.01023721788078547</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.003094519954174757</v>
+        <v>0.01168392319232225</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.008623962290585041</v>
+        <v>0.0290415845811367</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.00830517802387476</v>
+        <v>0.007396956440061331</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.002781431190669537</v>
+        <v>0.0001326967030763626</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01132130343466997</v>
+        <v>0.01801556348800659</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.006124591454863548</v>
+        <v>0.03345394879579544</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.008247140794992447</v>
+        <v>0.02036273665726185</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.004139411728829145</v>
+        <v>0.0006300443783402443</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01689843088388443</v>
+        <v>0.01320449635386467</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.009258629754185677</v>
+        <v>0.004490646533668041</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02467920258641243</v>
+        <v>0.006448993925005198</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.005586586892604828</v>
+        <v>0.00720611959695816</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.003323745215311646</v>
+        <v>0.003434648737311363</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.003609974635764956</v>
+        <v>0.02262180484831333</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.009100445546209812</v>
+        <v>0.01352742686867714</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.003311777021735907</v>
+        <v>0.01077302638441324</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01464041136205196</v>
+        <v>0.01046780403703451</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01104843243956566</v>
+        <v>0.01909568347036839</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.005266956984996796</v>
+        <v>0.007082951255142689</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.02368021942675114</v>
+        <v>0.02488790452480316</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.007363246753811836</v>
+        <v>0.006815139669924974</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.02162777818739414</v>
+        <v>0.006456607021391392</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.007312201894819736</v>
+        <v>0.008795415051281452</v>
       </c>
       <c r="EX13" t="n">
-        <v>6.725895218551159e-06</v>
+        <v>0.02465679869055748</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01067202165722847</v>
+        <v>0.02810896001756191</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.007616600953042507</v>
+        <v>0.005859690718352795</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.01543204393237829</v>
+        <v>0.0045985565520823</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004906177055090666</v>
+        <v>0.005389915779232979</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0141181256622076</v>
+        <v>0.01846372522413731</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.007462276145815849</v>
+        <v>0.004330689553171396</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.002147475956007838</v>
+        <v>0.003438889048993587</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.004191119689494371</v>
+        <v>0.001829314511269331</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0049867769703269</v>
+        <v>0.01314711291342974</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.009410449303686619</v>
+        <v>0.0401281863451004</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.006676018238067627</v>
+        <v>0.01993844285607338</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.009266789071261883</v>
+        <v>0.03171888366341591</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.004707095213234425</v>
+        <v>0.002234184183180332</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.011130690574646</v>
+        <v>0.02576791681349277</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.003824451472610235</v>
+        <v>0.008479271084070206</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.000258467742241919</v>
+        <v>0.004222590941935778</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.007327593863010406</v>
+        <v>0.02488220296800137</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.008672646246850491</v>
+        <v>0.009762185625731945</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.02538637258112431</v>
+        <v>0.1263723075389862</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01500134728848934</v>
+        <v>0.0113886371254921</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.04232219979166985</v>
+        <v>0.06760478764772415</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.009490863420069218</v>
+        <v>0.1198888570070267</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.007723568938672543</v>
+        <v>0.04969322681427002</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.005876758135855198</v>
+        <v>0.08352083712816238</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0008037179941311479</v>
+        <v>0.01876303181052208</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.003508075373247266</v>
+        <v>0.008728796616196632</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01534845307469368</v>
+        <v>0.002256445121020079</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01254548877477646</v>
+        <v>0.006199833936989307</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.007483052089810371</v>
+        <v>0.04496890679001808</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01295770611613989</v>
+        <v>0.03682685643434525</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0008133142255246639</v>
+        <v>0.0331462100148201</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.004628051538020372</v>
+        <v>0.02634149417281151</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.03829739987850189</v>
+        <v>0.003039675299078226</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.02968338690698147</v>
+        <v>0.01054034568369389</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0005091205239295959</v>
+        <v>0.01882053911685944</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5.840260200784542e-06</v>
+        <v>0.0005276508745737374</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001611776300705969</v>
+        <v>0.008239865303039551</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001754413533490151</v>
+        <v>0.001347625744529068</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0007946148980408907</v>
+        <v>0.01558158453553915</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003493639815133065</v>
+        <v>0.001682309317402542</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001524163235444576</v>
+        <v>0.004478043876588345</v>
       </c>
       <c r="G14" t="n">
-        <v>8.120201528072357e-05</v>
+        <v>0.01025102846324444</v>
       </c>
       <c r="H14" t="n">
-        <v>5.243229315965436e-05</v>
+        <v>0.008206908591091633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001522275124443695</v>
+        <v>0.002888838294893503</v>
       </c>
       <c r="J14" t="n">
-        <v>1.917568442877382e-05</v>
+        <v>0.0009910607477650046</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001232072827406228</v>
+        <v>0.01140448730438948</v>
       </c>
       <c r="L14" t="n">
-        <v>2.094503906846512e-05</v>
+        <v>0.001095952000468969</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0006701067322865129</v>
+        <v>0.0211777500808239</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004480703792069107</v>
+        <v>0.006586878560483456</v>
       </c>
       <c r="O14" t="n">
-        <v>8.582487498642877e-05</v>
+        <v>0.006758546456694603</v>
       </c>
       <c r="P14" t="n">
-        <v>3.932471008738503e-05</v>
+        <v>0.007887891493737698</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.000287225644569844</v>
+        <v>0.002023858483880758</v>
       </c>
       <c r="R14" t="n">
-        <v>1.292407432629261e-06</v>
+        <v>0.0019312429940328</v>
       </c>
       <c r="S14" t="n">
-        <v>8.668786176713184e-05</v>
+        <v>0.0002332738367840648</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0002497217792551965</v>
+        <v>0.0002244203351438046</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001413448480889201</v>
+        <v>0.0007310784421861172</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002143246674677357</v>
+        <v>0.002344283973798156</v>
       </c>
       <c r="W14" t="n">
-        <v>9.567733650328591e-05</v>
+        <v>0.002962898230180144</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0001774172706063837</v>
+        <v>0.00448631914332509</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.677708344999701e-05</v>
+        <v>0.001341392518952489</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.24165583960712e-05</v>
+        <v>0.004028945229947567</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.626001464203e-05</v>
+        <v>0.0001884110388346016</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.826601308304816e-05</v>
+        <v>0.002676823642104864</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.854186307871714e-05</v>
+        <v>0.001475232187658548</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.157683360972442e-05</v>
+        <v>0.000574154662899673</v>
       </c>
       <c r="AE14" t="n">
-        <v>6.88380459905602e-05</v>
+        <v>0.004929389804601669</v>
       </c>
       <c r="AF14" t="n">
-        <v>7.388762605842203e-05</v>
+        <v>0.00088492565555498</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001307128404732794</v>
+        <v>0.004691540729254484</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.942110924981534e-05</v>
+        <v>0.0006489546503871679</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001450746203772724</v>
+        <v>0.006497777532786131</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.015578163787723e-06</v>
+        <v>0.002594952937215567</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0001858196046669036</v>
+        <v>0.0007421846967190504</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.178495899192058e-05</v>
+        <v>0.00111627543810755</v>
       </c>
       <c r="AM14" t="n">
-        <v>4.709134736913256e-05</v>
+        <v>0.00172995135653764</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001546261773910373</v>
+        <v>0.005816450342535973</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0001962497626664117</v>
+        <v>0.000434978399425745</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0002476362860761583</v>
+        <v>0.003298629075288773</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.634011565940455e-05</v>
+        <v>0.001693538040854037</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001327445352217183</v>
+        <v>0.003860631259158254</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.644969860441051e-05</v>
+        <v>0.0006652517477050424</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.998432996217161e-05</v>
+        <v>0.0006432749796658754</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001040688715875149</v>
+        <v>0.01271562743932009</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.089436020469293e-05</v>
+        <v>4.431453999131918e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.004462920827791e-05</v>
+        <v>0.008464593440294266</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0001513866154709831</v>
+        <v>0.0108626764267683</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.976398435654119e-05</v>
+        <v>0.004139273893088102</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001130458549596369</v>
+        <v>0.0007695526001043618</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0002597544225864112</v>
+        <v>0.0006497842841781676</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0001130311284214258</v>
+        <v>0.003426406299695373</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.99018613784574e-05</v>
+        <v>0.0006682114908471704</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0002524264273233712</v>
+        <v>0.0001230000052601099</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0003415217215660959</v>
+        <v>0.001606471952982247</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0002707615494728088</v>
+        <v>0.0004967525601387024</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0006132024573162198</v>
+        <v>0.008099543862044811</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.000112440378870815</v>
+        <v>0.0009467240306548774</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0001155557401943952</v>
+        <v>0.002307189162820578</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002499907277524471</v>
+        <v>0.008147920481860638</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.104874122072943e-05</v>
+        <v>0.001291556283831596</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001537741045467556</v>
+        <v>0.0004600438696797937</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0002867828297894448</v>
+        <v>0.006507849786430597</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001231195492437109</v>
+        <v>0.000534822465851903</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.029658142215339e-05</v>
+        <v>0.003881267970427871</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0003041635791305453</v>
+        <v>0.003496648045256734</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001917651534313336</v>
+        <v>0.0005209803930483758</v>
       </c>
       <c r="BR14" t="n">
-        <v>7.914294837974012e-05</v>
+        <v>0.00436552707105875</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001489057904109359</v>
+        <v>0.002978261560201645</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.489324293099344e-05</v>
+        <v>0.001516190590336919</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001089590659830719</v>
+        <v>0.000953181937802583</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0005506206653080881</v>
+        <v>0.007154806982725859</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0001161650216090493</v>
+        <v>0.00169446412473917</v>
       </c>
       <c r="BX14" t="n">
-        <v>5.340867573977448e-06</v>
+        <v>0.009536284953355789</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0001166442307294346</v>
+        <v>0.00288027198985219</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0002596518024802208</v>
+        <v>0.004025486763566732</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.701932579744607e-05</v>
+        <v>0.002987797604873776</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.970118763798382e-06</v>
+        <v>0.001791962189599872</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.189393803244457e-05</v>
+        <v>0.0005559155251830816</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.534220715868287e-05</v>
+        <v>0.000451629952294752</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0002876692451536655</v>
+        <v>0.002534270519390702</v>
       </c>
       <c r="CF14" t="n">
-        <v>6.899289292050526e-05</v>
+        <v>4.756815178552642e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001009512561722659</v>
+        <v>0.005565492436289787</v>
       </c>
       <c r="CH14" t="n">
-        <v>7.313749665627256e-05</v>
+        <v>0.001118404325097799</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.516585118428338e-05</v>
+        <v>6.235702312551439e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001091029189410619</v>
+        <v>0.0007713603554293513</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.386168777476996e-05</v>
+        <v>0.0008455849019810557</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.13829698623158e-05</v>
+        <v>0.0004475276218727231</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0003885402693413198</v>
+        <v>0.003164241323247552</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0001476966426707804</v>
+        <v>0.009180929511785507</v>
       </c>
       <c r="CO14" t="n">
-        <v>3.98790325562004e-05</v>
+        <v>0.004724390339106321</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0001854877482401207</v>
+        <v>0.01036405470222235</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002317958715138957</v>
+        <v>0.002342243678867817</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0004661147249862552</v>
+        <v>0.0003147060051560402</v>
       </c>
       <c r="CS14" t="n">
-        <v>9.901042358251289e-05</v>
+        <v>0.002753692213445902</v>
       </c>
       <c r="CT14" t="n">
-        <v>9.785094152903184e-05</v>
+        <v>0.003018435556441545</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001629652251722291</v>
+        <v>0.001627282821573317</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.100866549881175e-05</v>
+        <v>4.863202047999948e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0002624926855787635</v>
+        <v>0.002254630904644728</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.000107135834696237</v>
+        <v>0.0002042313426500186</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.000139376541483216</v>
+        <v>0.006791092455387115</v>
       </c>
       <c r="CZ14" t="n">
-        <v>6.3276820583269e-05</v>
+        <v>0.0009295381023548543</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.197098936245311e-05</v>
+        <v>0.0002572032681200653</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001120261731557548</v>
+        <v>0.0007284341263584793</v>
       </c>
       <c r="DC14" t="n">
-        <v>8.111746865324676e-05</v>
+        <v>0.000431393418693915</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.684827657300048e-05</v>
+        <v>0.0002428658626740798</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001342394098173827</v>
+        <v>0.0004447015235200524</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0004595046339090914</v>
+        <v>0.000377421616576612</v>
       </c>
       <c r="DG14" t="n">
-        <v>7.173861376941204e-05</v>
+        <v>0.003355272812768817</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0004412890993990004</v>
+        <v>0.003704281989485025</v>
       </c>
       <c r="DI14" t="n">
-        <v>9.070959640666842e-05</v>
+        <v>0.0009069829829968512</v>
       </c>
       <c r="DJ14" t="n">
-        <v>9.093373591895215e-07</v>
+        <v>0.0004578861990012228</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.49531721137464e-05</v>
+        <v>0.0008498162496834993</v>
       </c>
       <c r="DL14" t="n">
-        <v>9.666496771387756e-05</v>
+        <v>0.009503497742116451</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001020778508973308</v>
+        <v>0.001389303477481008</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0001997000799747184</v>
+        <v>0.0006421543657779694</v>
       </c>
       <c r="DO14" t="n">
-        <v>9.873247472569346e-05</v>
+        <v>0.003678488079458475</v>
       </c>
       <c r="DP14" t="n">
-        <v>1.253701429959619e-05</v>
+        <v>0.0005762028740718961</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001295764523092657</v>
+        <v>0.001099423039704561</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0001358698355033994</v>
+        <v>0.000319569488056004</v>
       </c>
       <c r="DS14" t="n">
-        <v>4.817799344891682e-05</v>
+        <v>0.001956274965777993</v>
       </c>
       <c r="DT14" t="n">
-        <v>6.63617393001914e-05</v>
+        <v>0.003010112093761563</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.000169649749295786</v>
+        <v>0.005424900446087122</v>
       </c>
       <c r="DV14" t="n">
-        <v>3.262624159106053e-05</v>
+        <v>0.005687251221388578</v>
       </c>
       <c r="DW14" t="n">
-        <v>6.155388109618798e-05</v>
+        <v>0.001294135116040707</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001223982544615865</v>
+        <v>2.345655229873955e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.025315087754279e-05</v>
+        <v>0.0007988946745172143</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.540636680554599e-05</v>
+        <v>0.001722458284348249</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0002504037402104586</v>
+        <v>0.003652730491012335</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.00018369234749116</v>
+        <v>0.0005066295270808041</v>
       </c>
       <c r="EC14" t="n">
-        <v>9.22181861824356e-05</v>
+        <v>0.0006348177557811141</v>
       </c>
       <c r="ED14" t="n">
-        <v>2.88032169919461e-05</v>
+        <v>0.01042557880282402</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0001285430771531537</v>
+        <v>0.005765276961028576</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0002027324226219207</v>
+        <v>0.000269662617938593</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0002860151580534875</v>
+        <v>0.000501627626363188</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0001664316805545241</v>
+        <v>0.0007885171216912568</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001211349808727391</v>
+        <v>0.004760871641337872</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001538748474558815</v>
+        <v>0.001908444915898144</v>
       </c>
       <c r="EK14" t="n">
-        <v>1.950781370396726e-05</v>
+        <v>0.0009629462147131562</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001420683111064136</v>
+        <v>0.0003971244150307029</v>
       </c>
       <c r="EM14" t="n">
-        <v>6.617565668420866e-05</v>
+        <v>0.0003320339310448617</v>
       </c>
       <c r="EN14" t="n">
-        <v>6.655273864453193e-06</v>
+        <v>0.0009607006795704365</v>
       </c>
       <c r="EO14" t="n">
-        <v>6.501965981442481e-05</v>
+        <v>0.001167875248938799</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0002460824907757342</v>
+        <v>0.00135481683537364</v>
       </c>
       <c r="EQ14" t="n">
-        <v>6.920748273842037e-05</v>
+        <v>0.001650888239964843</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001428242394467816</v>
+        <v>0.005220805760473013</v>
       </c>
       <c r="ES14" t="n">
-        <v>6.347874295897782e-05</v>
+        <v>0.001295029418542981</v>
       </c>
       <c r="ET14" t="n">
-        <v>6.265864794841036e-05</v>
+        <v>0.00329115311615169</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0001648672041483223</v>
+        <v>0.003209303133189678</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0001089964134735055</v>
+        <v>0.0003931780811399221</v>
       </c>
       <c r="EW14" t="n">
-        <v>2.686264087969903e-05</v>
+        <v>0.004174626898020506</v>
       </c>
       <c r="EX14" t="n">
-        <v>7.300124707398936e-05</v>
+        <v>1.315159897785634e-05</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0002747240068856627</v>
+        <v>0.003187896683812141</v>
       </c>
       <c r="EZ14" t="n">
-        <v>7.342754543060437e-05</v>
+        <v>0.0001315240369876847</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0001324973127339035</v>
+        <v>0.007089988794177771</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.64191967289662e-05</v>
+        <v>0.0007446196977980435</v>
       </c>
       <c r="FC14" t="n">
-        <v>3.316194852232002e-05</v>
+        <v>0.0009314508060924709</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.000104663246020209</v>
+        <v>0.001787243876606226</v>
       </c>
       <c r="FE14" t="n">
-        <v>7.638049282832071e-05</v>
+        <v>0.00140296621248126</v>
       </c>
       <c r="FF14" t="n">
-        <v>4.558328510029241e-05</v>
+        <v>0.0007253037765622139</v>
       </c>
       <c r="FG14" t="n">
-        <v>7.205719884950668e-05</v>
+        <v>0.0009790189797058702</v>
       </c>
       <c r="FH14" t="n">
-        <v>2.09110148716718e-05</v>
+        <v>0.0009268978028558195</v>
       </c>
       <c r="FI14" t="n">
-        <v>9.939823939930648e-06</v>
+        <v>0.0006395233212970197</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0002068496687570587</v>
+        <v>0.004363651387393475</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0002316066675120965</v>
+        <v>0.0009627057006582618</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.000166366487974301</v>
+        <v>0.0007276845281012356</v>
       </c>
       <c r="FM14" t="n">
-        <v>6.402537110261619e-05</v>
+        <v>0.001046173856593668</v>
       </c>
       <c r="FN14" t="n">
-        <v>3.616604590206407e-05</v>
+        <v>0.0004351532261352986</v>
       </c>
       <c r="FO14" t="n">
-        <v>4.421700941747986e-05</v>
+        <v>0.0002001914544962347</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001693347003310919</v>
+        <v>0.003168048802763224</v>
       </c>
       <c r="FQ14" t="n">
-        <v>9.633083664084552e-07</v>
+        <v>0.0004847799427807331</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0003774623037315905</v>
+        <v>0.005916014313697815</v>
       </c>
       <c r="FS14" t="n">
-        <v>8.188743959181011e-05</v>
+        <v>0.002823577029630542</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001846301165642217</v>
+        <v>0.006099825259298086</v>
       </c>
       <c r="FU14" t="n">
-        <v>5.93784570810385e-05</v>
+        <v>0.002882726723328233</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001273428206332028</v>
+        <v>0.002048505004495382</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001311355881625786</v>
+        <v>0.005272627808153629</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002005021960940212</v>
+        <v>0.002922386862337589</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0001252066867891699</v>
+        <v>0.0003666744451038539</v>
       </c>
       <c r="FZ14" t="n">
-        <v>4.665816595661454e-05</v>
+        <v>0.001854271860793233</v>
       </c>
       <c r="GA14" t="n">
-        <v>2.345942448300775e-06</v>
+        <v>0.001521181431598961</v>
       </c>
       <c r="GB14" t="n">
-        <v>3.651975930551998e-05</v>
+        <v>0.004457834642380476</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001493508170824498</v>
+        <v>0.003507794346660376</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.000133145964355208</v>
+        <v>0.002822516253218055</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0001674088562140241</v>
+        <v>0.007606183644384146</v>
       </c>
       <c r="GF14" t="n">
-        <v>1.925840660987888e-05</v>
+        <v>1.249295019079e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001467221445636824</v>
+        <v>0.0005169855430722237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8.688907837495208e-05</v>
+        <v>0.005037402734160423</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02330350875854492</v>
+        <v>0.04219451546669006</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004421301186084747</v>
+        <v>0.00908135250210762</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01216900069266558</v>
+        <v>0.06069734320044518</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009954709559679031</v>
+        <v>0.0150535237044096</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00528914388269186</v>
+        <v>0.02359289303421974</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005678180605173111</v>
+        <v>0.02322280220687389</v>
       </c>
       <c r="H15" t="n">
-        <v>0.002746412297710776</v>
+        <v>0.03003676421940327</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001950877835042775</v>
+        <v>0.001411843695677817</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001712961471639574</v>
+        <v>0.0006440184079110622</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01783694140613079</v>
+        <v>0.04360752925276756</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001271940185688436</v>
+        <v>0.01138071902096272</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01074516773223877</v>
+        <v>0.08071862906217575</v>
       </c>
       <c r="N15" t="n">
-        <v>0.009928870014846325</v>
+        <v>0.003680619644001126</v>
       </c>
       <c r="O15" t="n">
-        <v>0.006941618863493204</v>
+        <v>0.02279254980385303</v>
       </c>
       <c r="P15" t="n">
-        <v>0.005444900132715702</v>
+        <v>0.0219925120472908</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0009814765071496367</v>
+        <v>0.002810830250382423</v>
       </c>
       <c r="R15" t="n">
-        <v>0.002021793508902192</v>
+        <v>0.0001027401303872466</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0007326342747546732</v>
+        <v>0.0001009544357657433</v>
       </c>
       <c r="T15" t="n">
-        <v>0.004328353796154261</v>
+        <v>0.005857315380126238</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0003185325185768306</v>
+        <v>0.000574780919123441</v>
       </c>
       <c r="V15" t="n">
-        <v>0.003282707650214434</v>
+        <v>0.00882086344063282</v>
       </c>
       <c r="W15" t="n">
-        <v>0.000781940936576575</v>
+        <v>0.01091164909303188</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002892100252211094</v>
+        <v>0.01399272680282593</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002695279195904732</v>
+        <v>0.0009798961691558361</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.003058093134313822</v>
+        <v>0.007368057034909725</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002945141401141882</v>
+        <v>0.002450942760333419</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0001288009807467461</v>
+        <v>0.006569628603756428</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.003311949549242854</v>
+        <v>0.00476369820535183</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0001071903316187672</v>
+        <v>0.00427351426333189</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0007436651503667235</v>
+        <v>0.01610767282545567</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.002518802881240845</v>
+        <v>0.003021130571141839</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001782765262760222</v>
+        <v>0.006284379400312901</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.002272121142596006</v>
+        <v>0.008170178160071373</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.001439796993508935</v>
+        <v>0.0006902656168676913</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.001893740729428828</v>
+        <v>0.01355918403714895</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0008400705992244184</v>
+        <v>0.002735625021159649</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.004671132657676935</v>
+        <v>0.005962332710623741</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.973479609470814e-05</v>
+        <v>0.003934012725949287</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.805885979905725e-05</v>
+        <v>0.02382302470505238</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.001231417059898376</v>
+        <v>0.008984040468931198</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.002077470067888498</v>
+        <v>0.01392064988613129</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001532997819595039</v>
+        <v>0.007685228250920773</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.001429874915629625</v>
+        <v>0.002437521703541279</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.001580546027980745</v>
+        <v>0.001850484288297594</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.002297412604093552</v>
+        <v>0.003182522486895323</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.01632418669760227</v>
+        <v>0.02837514318525791</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.001901729614473879</v>
+        <v>0.004616096615791321</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.003717947052791715</v>
+        <v>0.0331713855266571</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.004561092238873243</v>
+        <v>0.02354047633707523</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.001123810186982155</v>
+        <v>0.005349616520106792</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.001173813478089869</v>
+        <v>0.001903453376144171</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0003039761504624039</v>
+        <v>0.006071124225854874</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0008981006685644388</v>
+        <v>0.01233165711164474</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0005988160846754909</v>
+        <v>0.00562314735725522</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.003201056271791458</v>
+        <v>0.005403123330324888</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.003915607463568449</v>
+        <v>0.004744116216897964</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.00402331817895174</v>
+        <v>0.004018305335193872</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.007838740944862366</v>
+        <v>0.01811395771801472</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001463191001676023</v>
+        <v>0.01014070585370064</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.003792308503761888</v>
+        <v>0.003802469465881586</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.00108698639087379</v>
+        <v>0.01676118560135365</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.003181543666869402</v>
+        <v>0.01452455762773752</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.001560897100716829</v>
+        <v>0.005110134370625019</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.002367273438721895</v>
+        <v>0.002465987112373114</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.002215291373431683</v>
+        <v>0.004002691246569157</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0009016427793540061</v>
+        <v>0.008499188348650932</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0003890680382028222</v>
+        <v>0.004445213358849287</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.002607080154120922</v>
+        <v>0.003518895944580436</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0001427465758752078</v>
+        <v>0.006596869789063931</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.001273130066692829</v>
+        <v>0.002046052366495132</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.000699087860994041</v>
+        <v>0.002001280197873712</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.002224058378487825</v>
+        <v>0.006562060676515102</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.009866781532764435</v>
+        <v>0.02236493676900864</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.00470731919631362</v>
+        <v>0.002297333907335997</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.003825054038316011</v>
+        <v>0.0274430587887764</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.001573713263496757</v>
+        <v>0.006021340843290091</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.002302495529875159</v>
+        <v>0.01755275949835777</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.001417222549207509</v>
+        <v>0.006281350273638964</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.001309844781644642</v>
+        <v>0.0001722614979371428</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.002235280117020011</v>
+        <v>0.005234560929238796</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0001531103625893593</v>
+        <v>0.002307160757482052</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.003570882370695472</v>
+        <v>0.009195578284561634</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.001479489612393081</v>
+        <v>0.003399784909561276</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.001802493818104267</v>
+        <v>0.02104878053069115</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0003768401802517474</v>
+        <v>0.002125354949384928</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001969018252566457</v>
+        <v>0.001471389667131007</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0004765506891999394</v>
+        <v>0.0005128991906531155</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0006131354602985084</v>
+        <v>0.008740557357668877</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.001473666052334011</v>
+        <v>0.002702224534004927</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.003250881563872099</v>
+        <v>0.004988268949091434</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0006762659759260714</v>
+        <v>0.01368052791804075</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.049225193128223e-05</v>
+        <v>0.004831807222217321</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.001546477084048092</v>
+        <v>0.03386165574193001</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.001024697674438357</v>
+        <v>0.009733580984175205</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001777719298843294</v>
+        <v>0.0004003623034805059</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.003444449044764042</v>
+        <v>0.01075469329953194</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.003863171441480517</v>
+        <v>0.0009195829625241458</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0008992627263069153</v>
+        <v>0.008377586491405964</v>
       </c>
       <c r="CV15" t="n">
-        <v>9.59712197072804e-05</v>
+        <v>0.0006693201139569283</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.002790275495499372</v>
+        <v>0.008752099238336086</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.001631415216252208</v>
+        <v>0.002860801294445992</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.002303565852344036</v>
+        <v>0.02186433225870132</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0003019393770955503</v>
+        <v>0.0003482132742647082</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.002708815969526768</v>
+        <v>0.000100267025118228</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0002889665775001049</v>
+        <v>0.001032379572279751</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.000585174304433167</v>
+        <v>0.008090040646493435</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0005657839355990291</v>
+        <v>0.001551371533423662</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001480416394770145</v>
+        <v>0.004614184144884348</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.003362609539180994</v>
+        <v>0.009547608904540539</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0007210253970697522</v>
+        <v>0.002061845501884818</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.007637785281985998</v>
+        <v>0.01427384093403816</v>
       </c>
       <c r="DI15" t="n">
-        <v>4.100793739780784e-05</v>
+        <v>0.009354696609079838</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.003279248485341668</v>
+        <v>0.0009832549840211868</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.002381532918661833</v>
+        <v>0.0004922407679259777</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.001608547871001065</v>
+        <v>0.03000129386782646</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0005351657164283097</v>
+        <v>0.0050841742195189</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.001290869200602174</v>
+        <v>0.002412339206784964</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.001040036324411631</v>
+        <v>0.009715167805552483</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.00144451588857919</v>
+        <v>0.004819940775632858</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0009110490209423006</v>
+        <v>0.0113193467259407</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.002376485383138061</v>
+        <v>0.001101523521356285</v>
       </c>
       <c r="DS15" t="n">
-        <v>1.913149026222527e-05</v>
+        <v>0.008064006455242634</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.002733499277383089</v>
+        <v>0.01266114972531796</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.001745010958984494</v>
+        <v>0.0008135412354022264</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.002748001366853714</v>
+        <v>0.01542551815509796</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0006882736925035715</v>
+        <v>0.007224190980195999</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0002921770792454481</v>
+        <v>0.007681385613977909</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.003638271475210786</v>
+        <v>0.005835846997797489</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.002634477103129029</v>
+        <v>0.004127980209887028</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.002575881313532591</v>
+        <v>0.008068665862083435</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0006254918407648802</v>
+        <v>0.00559124443680048</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0007806052453815937</v>
+        <v>0.006736296229064465</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.001589431660249829</v>
+        <v>0.02621000073850155</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0008433000766672194</v>
+        <v>0.01740017160773277</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0009215408936142921</v>
+        <v>0.0004359509330242872</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.003061752300709486</v>
+        <v>0.01181088853627443</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.00158797309268266</v>
+        <v>0.0006342849228531122</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.001528120599687099</v>
+        <v>0.01702984049916267</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.001942378468811512</v>
+        <v>0.004033728502690792</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.003131240606307983</v>
+        <v>0.001111087272875011</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0004666747117880732</v>
+        <v>0.001261900644749403</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0003823384176939726</v>
+        <v>0.009030220098793507</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0004465500242076814</v>
+        <v>0.002775637898594141</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0002142945304512978</v>
+        <v>0.003146247006952763</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0009304818813689053</v>
+        <v>0.007987021468579769</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.00354575808160007</v>
+        <v>0.003170965705066919</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.001564952777698636</v>
+        <v>0.01780608855187893</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0001332212414126843</v>
+        <v>0.005453644786030054</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.004135077819228172</v>
+        <v>0.00701585877686739</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0007040382479317486</v>
+        <v>0.01573172584176064</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.002205654978752136</v>
+        <v>0.001572120003402233</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.000260670785792172</v>
+        <v>0.008988526649773121</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0004357374564278871</v>
+        <v>0.0009405958699062467</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.003009943291544914</v>
+        <v>0.01222422160208225</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001173617085441947</v>
+        <v>0.003214186523109674</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.00287058437243104</v>
+        <v>0.02416634559631348</v>
       </c>
       <c r="FB15" t="n">
-        <v>8.313386933878064e-05</v>
+        <v>0.0007095200708135962</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.00229626870714128</v>
+        <v>0.003363713389262557</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0007617789087817073</v>
+        <v>0.00215322757139802</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0004478669143281877</v>
+        <v>0.009331434033811092</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.001338567351922393</v>
+        <v>0.002492575673386455</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0005602504825219512</v>
+        <v>0.002643959131091833</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.002479432383552194</v>
+        <v>0.00673053739592433</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.002155710477381945</v>
+        <v>0.005919004790484905</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0009893428068608046</v>
+        <v>0.008501399308443069</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0006253025494515896</v>
+        <v>0.007755594328045845</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.00110330549068749</v>
+        <v>0.005887884180992842</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.001683054608292878</v>
+        <v>0.002845885464921594</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.000863581255543977</v>
+        <v>0.003811261616647243</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0005438961670733988</v>
+        <v>0.004510541446506977</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001028827391564846</v>
+        <v>0.0006064849440008402</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.004188145510852337</v>
+        <v>0.01245805341750383</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.00271155359223485</v>
+        <v>0.007131892256438732</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.006481397431343794</v>
+        <v>0.0003568325191736221</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0005268908571451902</v>
+        <v>0.01065503060817719</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.001106582349166274</v>
+        <v>0.005230084992945194</v>
       </c>
       <c r="FV15" t="n">
-        <v>6.105659122113138e-05</v>
+        <v>0.004204582422971725</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.001767536392435431</v>
+        <v>0.006367011461406946</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.0004698327684309334</v>
+        <v>0.006241001654416323</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.003353621112182736</v>
+        <v>0.009595952928066254</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0006680687074549496</v>
+        <v>0.004852414131164551</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0001133180630858988</v>
+        <v>0.008302124217152596</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.001706343144178391</v>
+        <v>0.01114752702414989</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001044055097736418</v>
+        <v>0.01716391742229462</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.001462967251427472</v>
+        <v>0.007764522451907396</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.008237233385443687</v>
+        <v>0.01666356809437275</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0007818093290552497</v>
+        <v>0.005109290592372417</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.00121690786909312</v>
+        <v>0.001615362358279526</v>
       </c>
     </row>
     <row r="16">
@@ -9534,1140 +9534,1140 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.003137419931590557</v>
+        <v>0.0009224746027030051</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1300564706325531</v>
+        <v>0.01799719966948032</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01567395403981209</v>
+        <v>0.005783058702945709</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06979529559612274</v>
+        <v>0.002165796933695674</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05861083418130875</v>
+        <v>0.008850079029798508</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07867868989706039</v>
+        <v>0.02516230754554272</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01225674897432327</v>
+        <v>0.001613723929040134</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04491782933473587</v>
+        <v>0.01407812535762787</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01140199322253466</v>
+        <v>0.001071125268936157</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01407503709197044</v>
+        <v>0.0007851977134123445</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1010492071509361</v>
+        <v>0.02799989841878414</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005205283407121897</v>
+        <v>0.0019748630002141</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04438605532050133</v>
+        <v>0.004313779529184103</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04619637131690979</v>
+        <v>0.01504225190728903</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08194314688444138</v>
+        <v>0.02731686271727085</v>
       </c>
       <c r="P17" t="n">
-        <v>0.009079907089471817</v>
+        <v>0.003417633939534426</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01044611539691687</v>
+        <v>0.004164135083556175</v>
       </c>
       <c r="R17" t="n">
-        <v>0.008981306105852127</v>
+        <v>0.003131637582555413</v>
       </c>
       <c r="S17" t="n">
-        <v>0.00601818785071373</v>
+        <v>0.002929305424913764</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02111065573990345</v>
+        <v>0.0005675688153132796</v>
       </c>
       <c r="U17" t="n">
-        <v>0.005207631271332502</v>
+        <v>0.003431976307183504</v>
       </c>
       <c r="V17" t="n">
-        <v>0.02143525704741478</v>
+        <v>0.005459708161652088</v>
       </c>
       <c r="W17" t="n">
-        <v>0.008035946637392044</v>
+        <v>0.005982423666864634</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01356285810470581</v>
+        <v>0.004083264153450727</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01027451641857624</v>
+        <v>0.0006704957922920585</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.005993585102260113</v>
+        <v>0.004397936165332794</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.008935686200857162</v>
+        <v>0.0003414481761865318</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.002221084199845791</v>
+        <v>0.006147040519863367</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01812519319355488</v>
+        <v>0.001402305439114571</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0009064630139619112</v>
+        <v>0.001360433059744537</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0003315721987746656</v>
+        <v>0.003852655179798603</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.003570022527128458</v>
+        <v>0.007074893452227116</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01073605939745903</v>
+        <v>0.002565843285992742</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.02170915156602859</v>
+        <v>0.004116109572350979</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.01331711560487747</v>
+        <v>0.008586723357439041</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005820499267429113</v>
+        <v>0.002407382940873504</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.01241196226328611</v>
+        <v>0.00270815915428102</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0229900237172842</v>
+        <v>0.003484311746433377</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.001622215146198869</v>
+        <v>0.002741825766861439</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.009949144907295704</v>
+        <v>0.005509212613105774</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.002511815866455436</v>
+        <v>0.006438162177801132</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.02000842988491058</v>
+        <v>0.0008744178921915591</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.004339692182838917</v>
+        <v>0.002655940596014261</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.01091425213962793</v>
+        <v>0.00573178194463253</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0172989834100008</v>
+        <v>0.001041821320541203</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.008701186627149582</v>
+        <v>0.002206249162554741</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.08718340843915939</v>
+        <v>0.02421092428267002</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.01070909574627876</v>
+        <v>0.002077536191791296</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.008975835517048836</v>
+        <v>0.001640592701733112</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.01426627673208714</v>
+        <v>0.002920926082879305</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.04718929529190063</v>
+        <v>0.01660799607634544</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.00401981407776475</v>
+        <v>0.0007832651608623564</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.03066841512918472</v>
+        <v>0.001544464845210314</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.01213336177170277</v>
+        <v>0.001659710658714175</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0001477794721722603</v>
+        <v>0.001515109557658434</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.02449808083474636</v>
+        <v>0.003328662365674973</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.02259453572332859</v>
+        <v>0.0004037914332002401</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.02386933192610741</v>
+        <v>0.001897698151879013</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0491013303399086</v>
+        <v>0.0005736332386732101</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.01501399464905262</v>
+        <v>0.0007571124006062746</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.01985669322311878</v>
+        <v>0.002268873155117035</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.02283438295125961</v>
+        <v>0.009247219190001488</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.006498557981103659</v>
+        <v>0.00445413077250123</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.01249305251985788</v>
+        <v>0.000541798654012382</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0299812275916338</v>
+        <v>0.01284836977720261</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.01414077542722225</v>
+        <v>0.001464299974031746</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.002807697514072061</v>
+        <v>0.002073660027235746</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01115695387125015</v>
+        <v>0.01024561189115047</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01047352515161037</v>
+        <v>0.006909005809575319</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.03159266710281372</v>
+        <v>0.008240810595452785</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.001354830805212259</v>
+        <v>0.002176776295527816</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.01423946116119623</v>
+        <v>0.003457420272752643</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.007796918042004108</v>
+        <v>0.003378799185156822</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.04947545751929283</v>
+        <v>0.01298754662275314</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.02839655429124832</v>
+        <v>0.0004757477436214685</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.01047027390450239</v>
+        <v>0.004331064410507679</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0137154059484601</v>
+        <v>0.0006705325213260949</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.008051357232034206</v>
+        <v>0.004785335157066584</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.007831617258489132</v>
+        <v>0.00149985495954752</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.01017947588115931</v>
+        <v>0.002327978843823075</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.009085055440664291</v>
+        <v>0.0009990244871005416</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0006633966695517302</v>
+        <v>0.002835174323990941</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.02159130945801735</v>
+        <v>0.004754246212542057</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.009947633370757103</v>
+        <v>0.00114776031114161</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.006417828146368265</v>
+        <v>0.000694172689691186</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0009292055619880557</v>
+        <v>0.002691558329388499</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.01228813640773296</v>
+        <v>0.007161590270698071</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.01293466053903103</v>
+        <v>0.00271274521946907</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.009342482313513756</v>
+        <v>0.0003518544544931501</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.005700182635337114</v>
+        <v>0.0007414208957925439</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.02051871083676815</v>
+        <v>0.0006053638644516468</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.01013607159256935</v>
+        <v>0.01423019263893366</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.003402518341317773</v>
+        <v>0.005539613775908947</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.02307109534740448</v>
+        <v>0.00212935172021389</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.006394322030246258</v>
+        <v>0.005814285017549992</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.01491891779005527</v>
+        <v>0.001834290800616145</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.02197131142020226</v>
+        <v>0.0005646609934046865</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.01202864106744528</v>
+        <v>2.975950701511465e-05</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.005094924941658974</v>
+        <v>0.002684345934540033</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0009791525080800056</v>
+        <v>0.001417165854945779</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.01728007942438126</v>
+        <v>0.004488235805183649</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.01192019414156675</v>
+        <v>0.0002264801878482103</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.01239949744194746</v>
+        <v>7.821782492101192e-05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.00227192067541182</v>
+        <v>0.002061133272945881</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.01592830754816532</v>
+        <v>0.007532935589551926</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.01261595916002989</v>
+        <v>0.0008937768870964646</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.01310401782393456</v>
+        <v>0.0001489084970671684</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.001294655725359917</v>
+        <v>0.0009208255214616656</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.01420615706592798</v>
+        <v>0.00020408327691257</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0166386179625988</v>
+        <v>0.01137759909033775</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0008580015273764729</v>
+        <v>0.004443620331585407</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.05776381492614746</v>
+        <v>0.008359231054782867</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.005356795620173216</v>
+        <v>0.001790491980500519</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.005463351495563984</v>
+        <v>0.000416460185078904</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.01432533841580153</v>
+        <v>0.001787085784599185</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.01642552018165588</v>
+        <v>0.005043763667345047</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.01557164546102285</v>
+        <v>0.003253110684454441</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.002139574149623513</v>
+        <v>0.005146594252437353</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.006987478584051132</v>
+        <v>0.002297459403052926</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.005467667244374752</v>
+        <v>0.002003709552809596</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.01362436451017857</v>
+        <v>0.007174336351454258</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.005807723384350538</v>
+        <v>0.006344430148601532</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.01723337545990944</v>
+        <v>0.0008429905865341425</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.004640231840312481</v>
+        <v>0.0008883068221621215</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.005265176296234131</v>
+        <v>0.004308345727622509</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.004311026073992252</v>
+        <v>0.00205677654594183</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.006610015407204628</v>
+        <v>0.004755419213324785</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.004845982883125544</v>
+        <v>0.001454448676668108</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0174206867814064</v>
+        <v>0.0006157176103442907</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.009001497179269791</v>
+        <v>0.001303420169278979</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.008738088421523571</v>
+        <v>0.0005365820834413171</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.002893803408369422</v>
+        <v>0.007122154347598553</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.009019685909152031</v>
+        <v>0.001992750680074096</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.001687305979430676</v>
+        <v>7.20962998457253e-06</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0009270915761590004</v>
+        <v>0.005062982439994812</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.005770767107605934</v>
+        <v>0.002833925653249025</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.01779798232018948</v>
+        <v>0.001058720634318888</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.009254125878214836</v>
+        <v>0.003346863435581326</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.01303812488913536</v>
+        <v>0.0003627341939136386</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01496103964745998</v>
+        <v>0.0007512944284826517</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.005573242902755737</v>
+        <v>0.009023579768836498</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.02080381475389004</v>
+        <v>0.001321504823863506</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.001685941591858864</v>
+        <v>0.00100401253439486</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0004034994635730982</v>
+        <v>0.0002483463031239808</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.002227042801678181</v>
+        <v>0.002906864508986473</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.006484291050583124</v>
+        <v>0.002282707486301661</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.02034709230065346</v>
+        <v>0.004857184365391731</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.009479411877691746</v>
+        <v>0.001549485605210066</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.005177534651011229</v>
+        <v>0.00332206953316927</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.01009145844727755</v>
+        <v>0.002314826939254999</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0136304059997201</v>
+        <v>0.0008705207728780806</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.02734759449958801</v>
+        <v>0.0001318236463703215</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.002649733796715736</v>
+        <v>0.0005366575205698609</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.001476698904298246</v>
+        <v>0.002448490355163813</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.01659040898084641</v>
+        <v>0.006083817221224308</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.008437030948698521</v>
+        <v>0.0008783507510088384</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.009800482541322708</v>
+        <v>0.0004725547041743994</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.001025364967063069</v>
+        <v>0.00113702763337642</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0137717816978693</v>
+        <v>0.006704856641590595</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0156711358577013</v>
+        <v>0.00270075211301446</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.01298864372074604</v>
+        <v>0.0007879198528826237</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.00642082653939724</v>
+        <v>0.0003343421558383852</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.005497205536812544</v>
+        <v>0.001037760521285236</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.008177455514669418</v>
+        <v>0.00554414838552475</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.01861674524843693</v>
+        <v>0.003714075544849038</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.02599779516458511</v>
+        <v>0.005362672731280327</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.005219506099820137</v>
+        <v>0.00181256013456732</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01249163225293159</v>
+        <v>0.0008713051211088896</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.007874947041273117</v>
+        <v>0.002508206525817513</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.00664625084027648</v>
+        <v>0.007380489725619555</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.01058685779571533</v>
+        <v>0.005377775058150291</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.007488060742616653</v>
+        <v>0.0004523111274465919</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.00812898576259613</v>
+        <v>0.001481588580645621</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.007874621078372002</v>
+        <v>0.008106169290840626</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.006472690962255001</v>
+        <v>0.005366268567740917</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.01515611540526152</v>
+        <v>0.001293645822443068</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01394194178283215</v>
+        <v>0.0004836953012272716</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.02380857244133949</v>
+        <v>0.0003406821051612496</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.007434505969285965</v>
+        <v>0.008977834135293961</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0007224921137094498</v>
+        <v>0.0001597401278559119</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.02364425919950008</v>
+        <v>0.003752990392968059</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.003790559247136116</v>
+        <v>0.001307342317886651</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.00186461373232305</v>
+        <v>0.002842501970008016</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.009597918018698692</v>
+        <v>0.0003721564135048538</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.01067049335688353</v>
+        <v>0.002586803399026394</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.01752031967043877</v>
+        <v>0.005885958205908537</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.05667661875486374</v>
+        <v>0.001467105466872454</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.002910698764026165</v>
+        <v>0.002862281166017056</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0009276373311877251</v>
+        <v>0.002284790389239788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0003989346150774509</v>
+        <v>5.261910700937733e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01311828847974539</v>
+        <v>3.147031384287402e-05</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001862356904894114</v>
+        <v>2.815814696077723e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004214293323457241</v>
+        <v>2.509955720597645e-06</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008136413060128689</v>
+        <v>1.502613304182887e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003640771145001054</v>
+        <v>3.950886821257882e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0007318351417779922</v>
+        <v>5.381752089306246e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001384300063364208</v>
+        <v>3.427945193834603e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0003423074376769364</v>
+        <v>3.121150484730606e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0006129470421001315</v>
+        <v>2.583252808108227e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009762544184923172</v>
+        <v>5.480041363625787e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0007845446234568954</v>
+        <v>1.976312341867015e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>0.002887876704335213</v>
+        <v>8.649294613860548e-06</v>
       </c>
       <c r="N18" t="n">
-        <v>0.00751650333404541</v>
+        <v>3.096835280302912e-05</v>
       </c>
       <c r="O18" t="n">
-        <v>0.003598944284021854</v>
+        <v>4.792843537870795e-05</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0008830545702949166</v>
+        <v>8.885177521733567e-06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.001484623760916293</v>
+        <v>2.46121362579288e-06</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0004619098326656967</v>
+        <v>1.474948567192769e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.000432682951213792</v>
+        <v>7.866925443522632e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.003065336961299181</v>
+        <v>4.928698672301834e-06</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0008944887667894363</v>
+        <v>1.056817563949153e-05</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001022580312564969</v>
+        <v>1.047510886564851e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0001497634802944958</v>
+        <v>7.790365998516791e-06</v>
       </c>
       <c r="X18" t="n">
-        <v>0.002157851587980986</v>
+        <v>9.917839633999392e-06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.000315193145070225</v>
+        <v>4.065972916578176e-06</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0004353400436230004</v>
+        <v>2.221394788648468e-05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.370081008644775e-05</v>
+        <v>6.313774065347388e-06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.001173353521153331</v>
+        <v>2.773232336039655e-05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002947400324046612</v>
+        <v>4.873894795309752e-06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0006698307697661221</v>
+        <v>8.210049600165803e-07</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0004048311675433069</v>
+        <v>1.920935937960166e-05</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0003678253851830959</v>
+        <v>2.031079202424735e-05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002075050491839647</v>
+        <v>7.003694918239489e-06</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.002033735159784555</v>
+        <v>1.159574640041683e-05</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0006476557464338839</v>
+        <v>2.760370443866123e-05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0001066690892912447</v>
+        <v>4.3624936552078e-07</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0012153364950791</v>
+        <v>5.485188921738882e-06</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.002302048495039344</v>
+        <v>8.711756890988909e-06</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0006295618368312716</v>
+        <v>8.424838597420603e-06</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.0001798754674382508</v>
+        <v>8.893438462109771e-06</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.001076487824320793</v>
+        <v>1.477889418310951e-05</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.002028871327638626</v>
+        <v>3.020230906258803e-06</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.001277786563150585</v>
+        <v>5.764652541984105e-06</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0004615198995452374</v>
+        <v>2.491710438334849e-05</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0006151511333882809</v>
+        <v>2.776317160169128e-06</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.001699312357231975</v>
+        <v>6.537943590956274e-06</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.01016157306730747</v>
+        <v>5.964191586826928e-05</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0009342236444354057</v>
+        <v>1.923885065480135e-06</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.0002996698603965342</v>
+        <v>1.206048096946688e-07</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.001741603715345263</v>
+        <v>1.172423981188331e-05</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.002988332649692893</v>
+        <v>3.239853322156705e-05</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.001750692958012223</v>
+        <v>6.081193532736506e-06</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.002003740519285202</v>
+        <v>1.063560034708644e-06</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.001390754943713546</v>
+        <v>6.723957994836383e-06</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.001263046870008111</v>
+        <v>1.754740151227452e-05</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.002877392806112766</v>
+        <v>1.030415296554565e-05</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.001226669293828309</v>
+        <v>6.080452294554561e-06</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.001580569078214467</v>
+        <v>6.640826086368179e-06</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.006617562845349312</v>
+        <v>8.369484930881299e-06</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.001009060768410563</v>
+        <v>6.992736871325178e-06</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.0002342055668123066</v>
+        <v>3.223928842999157e-06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.002690514549612999</v>
+        <v>2.66254210146144e-05</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.001164587796665728</v>
+        <v>1.537945718155243e-05</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.00167576246894896</v>
+        <v>5.71950658923015e-06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.004691668786108494</v>
+        <v>2.938107718364336e-05</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.001248026848770678</v>
+        <v>4.589164291246561e-06</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.0008554441155865788</v>
+        <v>5.768634309788467e-06</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.002503863070160151</v>
+        <v>2.286994276801124e-05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.00177878316026181</v>
+        <v>9.524351298750844e-06</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.001943471841514111</v>
+        <v>1.788844201655593e-05</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.0001202828934765421</v>
+        <v>1.449700266675791e-05</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.0006580410990864038</v>
+        <v>3.411087391214096e-06</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.001094235572963953</v>
+        <v>3.126012870779959e-06</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.005601409822702408</v>
+        <v>2.443514676997438e-05</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.003001623786985874</v>
+        <v>3.469105195108568e-06</v>
       </c>
       <c r="BX18" t="n">
-        <v>4.397193697514012e-05</v>
+        <v>1.995198545046151e-05</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.001295273075811565</v>
+        <v>2.939866590168094e-06</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.0008969554328359663</v>
+        <v>1.312907352257753e-05</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.0009093824774026871</v>
+        <v>2.600066409286228e-06</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.0008358529303222895</v>
+        <v>1.054134827427333e-05</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.0003896781418006867</v>
+        <v>1.254164203601249e-06</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.0002918815880548209</v>
+        <v>1.129355314333225e-05</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.002504711970686913</v>
+        <v>9.886070074571762e-06</v>
       </c>
       <c r="CF18" t="n">
-        <v>6.093362026149407e-05</v>
+        <v>7.757216735626571e-06</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.0008340605418197811</v>
+        <v>1.359870907435834e-06</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0004273569502402097</v>
+        <v>4.783604708791245e-06</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0005406179116107523</v>
+        <v>1.423934736521915e-05</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.0008612973615527153</v>
+        <v>7.067050773912342e-06</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.0001692404184723273</v>
+        <v>2.149076863133814e-06</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0002485023578628898</v>
+        <v>1.284529844269855e-06</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.003441284410655499</v>
+        <v>1.201739542011637e-05</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.002757104346528649</v>
+        <v>4.412533598951995e-05</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.000151832660776563</v>
+        <v>1.181253173854202e-05</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.001405001385137439</v>
+        <v>2.004526095333858e-06</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0007442885544151068</v>
+        <v>1.62485011969693e-05</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.001322290860116482</v>
+        <v>9.104262517212192e-07</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0007855653529986739</v>
+        <v>4.409918801684398e-06</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.001313596381805837</v>
+        <v>1.966844592971029e-06</v>
       </c>
       <c r="CU18" t="n">
-        <v>5.415478517534211e-05</v>
+        <v>6.184710855450248e-06</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.0002321984648006037</v>
+        <v>8.564882591599599e-06</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.00190496735740453</v>
+        <v>8.209963198169135e-06</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.0005686738877557218</v>
+        <v>6.351536285365e-06</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.0015002895379439</v>
+        <v>4.207819984003436e-06</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.0002670521789696068</v>
+        <v>9.885113740892848e-07</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.0009903896134346724</v>
+        <v>1.3660721378983e-05</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.0006464826292358339</v>
+        <v>1.867133050836856e-06</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0003590632986743003</v>
+        <v>3.672786988317966e-06</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.0003894047695212066</v>
+        <v>4.667242592404364e-08</v>
       </c>
       <c r="DE18" t="n">
-        <v>2.059072721749544e-05</v>
+        <v>7.079644092300441e-06</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.004651850089430809</v>
+        <v>1.515046278655063e-05</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.0009825638262555003</v>
+        <v>1.890554085548501e-05</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.003522638464346528</v>
+        <v>1.199329858536657e-06</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.000816927058622241</v>
+        <v>1.346737917629071e-05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>9.883810707833618e-05</v>
+        <v>7.566283784399275e-06</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.002810106379911304</v>
+        <v>1.402315956511302e-05</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.001000962685793638</v>
+        <v>3.076408574997913e-06</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.001805837266147137</v>
+        <v>2.586666823845007e-06</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.000796817010268569</v>
+        <v>1.609002538316417e-06</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.002175745088607073</v>
+        <v>7.786838068568613e-06</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.0006339072715491056</v>
+        <v>7.02691841070191e-06</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.0003275419003330171</v>
+        <v>1.737411730573513e-05</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0005163581809028983</v>
+        <v>1.398778658767696e-05</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.002848947886377573</v>
+        <v>1.858938730947557e-06</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.0003127810196019709</v>
+        <v>6.020974524290068e-06</v>
       </c>
       <c r="DU18" t="n">
-        <v>5.498501195688732e-06</v>
+        <v>2.15411728277104e-05</v>
       </c>
       <c r="DV18" t="n">
-        <v>0.001015286659821868</v>
+        <v>1.19657238428772e-06</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.00022822932805866</v>
+        <v>5.687072643922875e-06</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.792573837330565e-05</v>
+        <v>2.286897824888001e-06</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0003019040741492063</v>
+        <v>1.24832540677744e-05</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.0003592930152080953</v>
+        <v>7.182029548857827e-07</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.001747512724250555</v>
+        <v>1.077855586117948e-06</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.001319456030614674</v>
+        <v>1.416747909388505e-05</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.0002076134260278195</v>
+        <v>3.010642330991686e-06</v>
       </c>
       <c r="ED18" t="n">
-        <v>0.0004089793947059661</v>
+        <v>2.689764642127557e-06</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.000271331547992304</v>
+        <v>1.45312687891419e-05</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.0007362181786447763</v>
+        <v>1.11526633190806e-05</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.001087584416382015</v>
+        <v>3.319031975479447e-06</v>
       </c>
       <c r="EH18" t="n">
-        <v>0.0002890962932724506</v>
+        <v>7.84393705544062e-06</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.0002523866714909673</v>
+        <v>1.724509615996794e-06</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0009509776718914509</v>
+        <v>6.740553999406984e-06</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.0007004751823842525</v>
+        <v>2.018445957219228e-05</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.001340852468274534</v>
+        <v>4.373716819827678e-06</v>
       </c>
       <c r="EM18" t="n">
-        <v>7.972334424266592e-05</v>
+        <v>7.638748684257735e-06</v>
       </c>
       <c r="EN18" t="n">
-        <v>0.0005870854947715998</v>
+        <v>3.354028876856319e-07</v>
       </c>
       <c r="EO18" t="n">
-        <v>0.001643777824938297</v>
+        <v>9.267854693462141e-06</v>
       </c>
       <c r="EP18" t="n">
-        <v>8.788547711446881e-05</v>
+        <v>3.252717988289078e-06</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.001416048849932849</v>
+        <v>4.768793587572873e-06</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.001837005373090506</v>
+        <v>1.424457877874374e-05</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0003401536087039858</v>
+        <v>7.272716175066307e-06</v>
       </c>
       <c r="ET18" t="n">
-        <v>3.853182715829462e-05</v>
+        <v>6.181121079862351e-06</v>
       </c>
       <c r="EU18" t="n">
-        <v>0.0004211629275232553</v>
+        <v>6.095522167015588e-06</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.0009801588021218777</v>
+        <v>1.40732709041913e-07</v>
       </c>
       <c r="EW18" t="n">
-        <v>0.0006562088383361697</v>
+        <v>1.183605218102457e-05</v>
       </c>
       <c r="EX18" t="n">
-        <v>0.0003675704647321254</v>
+        <v>9.911294910125434e-06</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.001655303873121738</v>
+        <v>1.395982144458685e-05</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0.0001225298037752509</v>
+        <v>6.352439413603861e-06</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.0008327101822942495</v>
+        <v>1.954088020283962e-06</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.0002434558555250987</v>
+        <v>1.751565378071973e-06</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.001102872658520937</v>
+        <v>1.208959656651132e-05</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.000980085926130414</v>
+        <v>6.53020015306538e-06</v>
       </c>
       <c r="FE18" t="n">
-        <v>0.0003355113440193236</v>
+        <v>3.285533693997422e-07</v>
       </c>
       <c r="FF18" t="n">
-        <v>5.443445115815848e-05</v>
+        <v>1.551974605717987e-06</v>
       </c>
       <c r="FG18" t="n">
-        <v>0.0005135565879754722</v>
+        <v>2.086791255351272e-06</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.00111302500590682</v>
+        <v>1.348462865280453e-05</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.0008865450508892536</v>
+        <v>9.016408512252383e-06</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.00114555936306715</v>
+        <v>1.208771573146805e-05</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.001266017090529203</v>
+        <v>2.37348740483867e-06</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.001337180030532181</v>
+        <v>9.194254744215868e-07</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.0002620020241010934</v>
+        <v>7.859337529225741e-06</v>
       </c>
       <c r="FN18" t="n">
-        <v>0.0004555796040222049</v>
+        <v>2.043358290393371e-05</v>
       </c>
       <c r="FO18" t="n">
-        <v>0.0007945887045934796</v>
+        <v>2.089374902425334e-06</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.002079748781397939</v>
+        <v>5.268889253784437e-07</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.0006572204292751849</v>
+        <v>1.158476425189292e-05</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0003920175950042903</v>
+        <v>1.759802762535401e-05</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.00193249131552875</v>
+        <v>8.12861617305316e-06</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.002351499628275633</v>
+        <v>4.598631221597316e-06</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.001097009517252445</v>
+        <v>1.919699570862576e-06</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.0007783902110531926</v>
+        <v>9.012920600071084e-06</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.0001865677768364549</v>
+        <v>1.671530299063306e-05</v>
       </c>
       <c r="FX18" t="n">
-        <v>0.0008046197472140193</v>
+        <v>2.267329546157271e-05</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.001738254562951624</v>
+        <v>1.464257184125017e-05</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.001529795117676258</v>
+        <v>1.733708631945774e-05</v>
       </c>
       <c r="GA18" t="n">
-        <v>0.001328108250163496</v>
+        <v>1.11026456579566e-05</v>
       </c>
       <c r="GB18" t="n">
-        <v>5.753863661084324e-05</v>
+        <v>4.242635895934654e-07</v>
       </c>
       <c r="GC18" t="n">
-        <v>5.135079845786095e-06</v>
+        <v>2.011830474657472e-05</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.002007258590310812</v>
+        <v>1.583749690325931e-05</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.001771380542777479</v>
+        <v>1.19169135359698e-06</v>
       </c>
       <c r="GF18" t="n">
-        <v>0.001483196625486016</v>
+        <v>9.290346497436985e-06</v>
       </c>
       <c r="GG18" t="n">
-        <v>0.0006132113630883396</v>
+        <v>1.19914029710344e-05</v>
       </c>
     </row>
   </sheetData>
